--- a/ClassMaterial/1차 프로젝트/6. API설계/6._API설계(김현규)ver-2.1.xlsx
+++ b/ClassMaterial/1차 프로젝트/6. API설계/6._API설계(김현규)ver-2.1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DW-203\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KHK\JavaClass\ClassMaterial\1차 프로젝트\6. API설계\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D1A695-F6A2-417A-B9E4-995989981155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12285"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +19,389 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>HyunKyu KIM</author>
+  </authors>
+  <commentList>
+    <comment ref="I23" authorId="0" shapeId="0" xr:uid="{BE11AFF7-CAA1-483B-AC33-557950AD60D6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HyunKyu KIM:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>기존</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">) dashboard.html
+(model: streamUrl,
+ptzState,
+message)
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I24" authorId="0" shapeId="0" xr:uid="{2C52E905-7342-48B5-B804-7FD91F4C4252}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HyunKyu KIM:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>기존</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>)dashboard.html
+(model: petId,
+nightModeEnabled,
+message)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I25" authorId="0" shapeId="0" xr:uid="{8BE1ED1B-E67C-4A33-A4F2-43FB3D7F0932}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HyunKyu KIM:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>기존</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>)dashboard.html
+(model: petId,
+audioState,
+message)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I26" authorId="0" shapeId="0" xr:uid="{ABB05FE7-C645-4799-85EF-F02A8AD658DE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HyunKyu KIM:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>기존</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>)dashboard.html
+(model: petId,
+feedResult,
+lastFeedAt,
+message)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I27" authorId="0" shapeId="0" xr:uid="{BBC9EDCD-9436-42AE-8655-242ECD6E0435}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HyunKyu KIM:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>기존</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>) dashboard.html
+(model: petId,
+capturedMediaId,
+thumbnailUrl,
+message)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I28" authorId="0" shapeId="0" xr:uid="{B0688690-4D9F-4D60-9827-2BF306ECDB6B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HyunKyu KIM:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>기존</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>) dashboard.html
+(model: petId,
+recordStatus,
+message)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I49" authorId="0" shapeId="0" xr:uid="{A1E0D86B-9428-43BE-8DEE-7962E189DA2D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HyunKyu KIM:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>기존</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>) admin-logs.html
+(model: logList,
+filter,
+pageInfo)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J49" authorId="0" shapeId="0" xr:uid="{FE4A5F91-1A65-4919-BAC9-C4AD7544B5E5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>HyunKyu KIM:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>기존</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>) admin-logs.html
+(model: {logList:[{logId:101,type:'ALERT',level:'HIGH'}],
+filter:{type:'alert'},
+pageInfo:{page:1,total:40}})</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="384">
   <si>
     <t>API 설계</t>
   </si>
@@ -553,14 +935,7 @@
 (model: {message:'비밀번호가 변경되었습니다.'})</t>
   </si>
   <si>
-    <t>대시보드 API
-(현규)</t>
-  </si>
-  <si>
     <t>dash-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">대시보드 메인 페이지 조회 </t>
   </si>
   <si>
     <t>/dashboard</t>
@@ -594,28 +969,16 @@
     <t>dash-002</t>
   </si>
   <si>
-    <t>실시간 영상 조회 및 PTZ 제어</t>
-  </si>
-  <si>
     <t>/dashboard/stream</t>
   </si>
   <si>
     <t>GET/POST</t>
   </si>
   <si>
-    <t>대시보드에서 영상 영역을 렌더링하고, 컨트롤러를 통해 카메라 각도를 상하좌우로 조절하고, 화면 확대/축소를 제어한다.</t>
-  </si>
-  <si>
     <t>petId, ptzCommand</t>
   </si>
   <si>
     <t>petId=1&amp;ptzCommand=LEFT</t>
-  </si>
-  <si>
-    <t>dashboard.html
-(model: streamUrl,
-ptzState,
-message)</t>
   </si>
   <si>
     <t>dashboard.html
@@ -633,19 +996,10 @@
     <t>/dashboard/night-mode</t>
   </si>
   <si>
-    <t>대시보드에서 야간모드 활성화/비활성화를 처리한다.</t>
-  </si>
-  <si>
     <t>petId, enabled</t>
   </si>
   <si>
     <t>petId=1&amp;enabled=true</t>
-  </si>
-  <si>
-    <t>dashboard.html
-(model: petId,
-nightModeEnabled,
-message)</t>
   </si>
   <si>
     <t>dashboard.html
@@ -673,12 +1027,6 @@
   </si>
   <si>
     <t>dashboard.html
-(model: petId,
-audioState,
-message)</t>
-  </si>
-  <si>
-    <t>dashboard.html
 (model: {petId:1,
 audioState:'START',
 message:'양방향 오디오가 시작되었습니다.'})</t>
@@ -700,13 +1048,6 @@
   </si>
   <si>
     <t>petId=1&amp;amount=30</t>
-  </si>
-  <si>
-    <t>dashboard.html
-(model: petId,
-feedResult,
-lastFeedAt,
-message)</t>
   </si>
   <si>
     <t>dashboard.html
@@ -725,17 +1066,7 @@
     <t>/dashboard/capture</t>
   </si>
   <si>
-    <t>현재 관제 화면 캡처 저장 요청을 처리하고, 갤러리에 갱신한다.</t>
-  </si>
-  <si>
     <t>petId=1</t>
-  </si>
-  <si>
-    <t>dashboard.html
-(model: petId,
-capturedMediaId,
-thumbnailUrl,
-message)</t>
   </si>
   <si>
     <t>dashboard.html
@@ -764,12 +1095,6 @@
   </si>
   <si>
     <t>dashboard.html
-(model: petId,
-recordStatus,
-message)</t>
-  </si>
-  <si>
-    <t>dashboard.html
 (model: {petId:1,
 recordStatus:'START',
 message:'녹화를 시작했습니다.'})</t>
@@ -1191,9 +1516,6 @@
 (flash: '이벤트 임계값 설정이 저장되었습니다.')</t>
   </si>
   <si>
-    <t>관리자 API</t>
-  </si>
-  <si>
     <t>admin-001</t>
   </si>
   <si>
@@ -1201,9 +1523,6 @@
   </si>
   <si>
     <t>/admin/pets</t>
-  </si>
-  <si>
-    <t>관리자 반려동물 목록 화면을 제공한다.</t>
   </si>
   <si>
     <t>keyword, page</t>
@@ -1230,23 +1549,10 @@
     <t>admin-002</t>
   </si>
   <si>
-    <t>전체 반려동물 상세</t>
-  </si>
-  <si>
     <t>/admin/pets/{petId}</t>
   </si>
   <si>
-    <t>특정 반려동물의 상세 정보와 수정 폼 화면을 렌더링한다.</t>
-  </si>
-  <si>
     <t>/admin/pets/1</t>
-  </si>
-  <si>
-    <t>admin-pet-detail.html
-(model: petDetail,
-ownerInfo,
-deviceList)
-또는 redirect:/admin/pets</t>
   </si>
   <si>
     <t>admin-pet-detail.html
@@ -1258,51 +1564,16 @@
     <t>admin-003</t>
   </si>
   <si>
-    <t>전체 반려동물 수정</t>
-  </si>
-  <si>
     <t>/admin/pets/{petId}/edit</t>
   </si>
   <si>
-    <t>관리자가 변경한 반려동물 정보(폼 제출)를 DB에 반영한다.</t>
-  </si>
-  <si>
-    <t>type, level, date</t>
-  </si>
-  <si>
-    <t>/admin/logs?type=alert</t>
-  </si>
-  <si>
-    <t>redirect:/admin/pets/{petId}
-또는 admin-pet-detail.html
-(model: petDetail,
-validationErrors,
-message)</t>
-  </si>
-  <si>
-    <t>성공 → redirect:/admin/pets/1
-실패 → admin-pet-detail.html
-(model: {petDetail:{petId:1,name:'보리'},
-validationErrors:['breed'],
-message:'품종을 입력해주세요.'})</t>
-  </si>
-  <si>
     <t>admin-004</t>
   </si>
   <si>
-    <t>전체 반려동물 삭제</t>
-  </si>
-  <si>
     <t>/admin/pets/{petId}/delete</t>
   </si>
   <si>
-    <t>특정 반려동물 데이터를 삭제 처리한다.</t>
-  </si>
-  <si>
     <t>logId</t>
-  </si>
-  <si>
-    <t>/admin/logs/100</t>
   </si>
   <si>
     <t>redirect:/admin/pets
@@ -1322,21 +1593,6 @@
     <t>/admin/logs</t>
   </si>
   <si>
-    <t>시스템 전체 로그를 등급 및 이벤트별로 필터링하여 조회한다.</t>
-  </si>
-  <si>
-    <t>admin-logs.html
-(model: logList,
-filter,
-pageInfo)</t>
-  </si>
-  <si>
-    <t>admin-logs.html
-(model: {logList:[{logId:101,type:'ALERT',level:'HIGH'}],
-filter:{type:'alert'},
-pageInfo:{page:1,total:40}})</t>
-  </si>
-  <si>
     <t>admin-006</t>
   </si>
   <si>
@@ -1344,9 +1600,6 @@
   </si>
   <si>
     <t>/admin/logs/{logId}</t>
-  </si>
-  <si>
-    <t>선택한 로그 상세 화면을 조회한다.</t>
   </si>
   <si>
     <t>/admin/logs/101</t>
@@ -1373,21 +1626,7 @@
     <t>/admin/users/{userId}/role</t>
   </si>
   <si>
-    <t>관리자가 사용자 권한 변경(일반/관리자/휴면)을 처리한다.</t>
-  </si>
-  <si>
-    <t>userId, 권한</t>
-  </si>
-  <si>
     <t>userId=3&amp;role=ADMIN</t>
-  </si>
-  <si>
-    <t>redirect:/admin/users/{userId}
-(flash: message)</t>
-  </si>
-  <si>
-    <t>redirect:/admin/users/3
-(flash: '사용자 권한이 ADMIN으로 변경되었습니다.')</t>
   </si>
   <si>
     <t>시뮬레이션 API</t>
@@ -1439,12 +1678,2348 @@
     <t>redirect:/admin/simulation/states?petId=1
 (flash: '총 10건의 상태데이터 시뮬레이션을 실행했습니다.')</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>대시보드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> API
+(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>현규</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>대시보드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>메인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>페이지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>조회</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>실시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>영상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>조회</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> PTZ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제어</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>대시보드에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>영상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>영역을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>렌더링하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>컨트롤러를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>통해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>카메라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>각도를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>상하좌우로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>조절하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>화면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>확대</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>축소를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제어한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>대시보드에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>야간모드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>활성화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>비활성화를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>처리한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>현재</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>관제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>화면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>캡처</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>저장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>요청을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>처리하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>갤러리에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>갱신한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>관리자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> API</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>관리자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>반려동물</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>목록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>화면을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제공한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>관리자</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>전체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>반려동물</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>상세</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>특정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>반려동물의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>상세</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>정보와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>수정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>폼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>화면을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>렌더링한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>전체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>반려동물</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>수정</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>관리자가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>변경한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>반려동물</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>정보</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>폼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제출</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>반영한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>전체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>반려동물</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>삭제</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>특정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>반려동물</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>데이터를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>삭제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>처리한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>시스템</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>전체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>로그를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>등급</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이벤트별로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>필터링하여</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>조회한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>선택한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>로그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>상세</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>화면을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>조회한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>관리자가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사용자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>권한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>변경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>일반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>관리자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>휴면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>처리한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>{ "success", "ptzState", "message" }</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "success", "nightModeEnabled", "message" }</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "success", "audioState", "message" }</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "success", "feedResult", "lastFeedAt", "message" }</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "success", "capturedMediaId", "thumbnailUrl", "message" }</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "success", "recordStatus", "message" }</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{success, userId, updatedRole, message}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{"success":true, "userId":3, "updatedRole":"ADMIN", "message":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>권한이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변경되었습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>."}</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{success, logList, pageInfo, filter}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"success":true, "logList":[...], "pageInfo":{"total":40}, "filter":{"type":"alert"}}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>petId, name, species, breed, age, weight, gender</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>userId, role</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>petId</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>admin-pet-detail.html
+(model: petDetail,
+ownerInfo)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>name=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보리&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>age=5&amp;weight=7.5</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성공</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → redirect:/admin/pets/1
+(flash:  '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정보가 수정되었습니다.')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실패</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → admin-pet-detail.html
+(model: {petDetail:{petId:1,name:'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'},
+validationErrors:['breed'],
+message:'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>품종을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>입력해주세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.'})</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>redirect:/admin/pets/{petId}
+(flash: message)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>petId=1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>type, level, date, page?</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>/admin/logs?type=ALERT&amp;level=HIGH</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1491,14 +4066,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1559,6 +4126,54 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1584,7 +4199,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="44">
     <border>
       <left/>
       <right/>
@@ -1678,21 +4293,6 @@
         <color indexed="64"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1926,19 +4526,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -2141,6 +4728,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2150,11 +4785,11 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2168,290 +4803,277 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Hyperlink" xfId="3"/>
-    <cellStyle name="나쁨" xfId="2"/>
-    <cellStyle name="좋음" xfId="1"/>
+    <cellStyle name="Hyperlink" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="나쁨" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="좋음" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2642,50 +5264,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" style="84" customWidth="1"/>
-    <col min="2" max="2" width="12" style="14" customWidth="1"/>
-    <col min="3" max="3" width="26.5703125" style="14" customWidth="1"/>
-    <col min="4" max="4" width="27" style="14" customWidth="1"/>
-    <col min="5" max="5" width="11" style="14" customWidth="1"/>
-    <col min="6" max="6" width="28" style="14" customWidth="1"/>
-    <col min="7" max="7" width="32" style="14" customWidth="1"/>
-    <col min="8" max="8" width="40" style="14" customWidth="1"/>
-    <col min="9" max="9" width="28" style="14" customWidth="1"/>
-    <col min="10" max="10" width="42" style="14" customWidth="1"/>
-    <col min="11" max="11" width="8" style="84" customWidth="1"/>
+    <col min="1" max="1" width="16" style="67" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="26.5703125" customWidth="1"/>
+    <col min="4" max="4" width="27" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
+    <col min="10" max="10" width="42" customWidth="1"/>
+    <col min="11" max="11" width="8" style="67" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="102"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="73"/>
     </row>
     <row r="2" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A2" s="103"/>
-      <c r="B2" s="104"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
-      <c r="F2" s="104"/>
-      <c r="G2" s="104"/>
-      <c r="H2" s="104"/>
-      <c r="I2" s="104"/>
-      <c r="J2" s="104"/>
-      <c r="K2" s="105"/>
+      <c r="A2" s="74"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="76"/>
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A3" s="2" t="s">
@@ -2723,137 +5345,137 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="94.5" customHeight="1" thickBot="1">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="B4" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="54" t="s">
+      <c r="D4" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="53" t="s">
+      <c r="E4" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="53" t="s">
+      <c r="F4" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="53" t="s">
+      <c r="G4" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="53" t="s">
+      <c r="H4" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="53" t="s">
+      <c r="I4" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="53" t="s">
+      <c r="J4" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="25" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="95.25" customHeight="1" thickBot="1">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="56" t="s">
+      <c r="C5" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="57" t="s">
+      <c r="D5" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="58" t="s">
+      <c r="E5" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="57" t="s">
+      <c r="F5" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="57" t="s">
+      <c r="G5" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="59" t="s">
+      <c r="H5" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="60" t="s">
+      <c r="I5" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="61" t="s">
+      <c r="J5" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="56.1" customHeight="1">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="82" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="45" t="s">
+      <c r="E6" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="44" t="s">
+      <c r="G6" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="44" t="s">
+      <c r="H6" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="I6" s="46" t="s">
+      <c r="I6" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="47" t="s">
+      <c r="J6" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A7" s="93"/>
-      <c r="B7" s="20" t="s">
+      <c r="A7" s="83"/>
+      <c r="B7" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="22" t="s">
+      <c r="H7" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="33" t="s">
+      <c r="J7" s="23" t="s">
         <v>43</v>
       </c>
       <c r="K7" s="5" t="s">
@@ -2861,32 +5483,32 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A8" s="93"/>
-      <c r="B8" s="20" t="s">
+      <c r="A8" s="83"/>
+      <c r="B8" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="33" t="s">
+      <c r="J8" s="23" t="s">
         <v>49</v>
       </c>
       <c r="K8" s="5" t="s">
@@ -2894,32 +5516,32 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A9" s="93"/>
-      <c r="B9" s="20" t="s">
+      <c r="A9" s="83"/>
+      <c r="B9" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="H9" s="22" t="s">
+      <c r="H9" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="J9" s="33" t="s">
+      <c r="J9" s="23" t="s">
         <v>57</v>
       </c>
       <c r="K9" s="5" t="s">
@@ -2927,32 +5549,32 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A10" s="93"/>
-      <c r="B10" s="20" t="s">
+      <c r="A10" s="83"/>
+      <c r="B10" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="I10" s="19" t="s">
+      <c r="I10" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="J10" s="34" t="s">
+      <c r="J10" s="24" t="s">
         <v>65</v>
       </c>
       <c r="K10" s="5" t="s">
@@ -2960,32 +5582,32 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A11" s="93"/>
-      <c r="B11" s="20" t="s">
+      <c r="A11" s="83"/>
+      <c r="B11" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="H11" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="I11" s="19" t="s">
+      <c r="I11" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="J11" s="34" t="s">
+      <c r="J11" s="24" t="s">
         <v>73</v>
       </c>
       <c r="K11" s="5" t="s">
@@ -2993,32 +5615,32 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="107.25" customHeight="1">
-      <c r="A12" s="93"/>
-      <c r="B12" s="20" t="s">
+      <c r="A12" s="83"/>
+      <c r="B12" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="H12" s="16" t="s">
+      <c r="H12" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="J12" s="33" t="s">
+      <c r="J12" s="23" t="s">
         <v>80</v>
       </c>
       <c r="K12" s="5" t="s">
@@ -3026,32 +5648,32 @@
       </c>
     </row>
     <row r="13" spans="1:11" ht="56.1" customHeight="1">
-      <c r="A13" s="93"/>
-      <c r="B13" s="20" t="s">
+      <c r="A13" s="83"/>
+      <c r="B13" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="I13" s="15" t="s">
+      <c r="I13" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="J13" s="33" t="s">
+      <c r="J13" s="23" t="s">
         <v>86</v>
       </c>
       <c r="K13" s="5" t="s">
@@ -3059,1344 +5681,1344 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A14" s="94"/>
-      <c r="B14" s="48" t="s">
+      <c r="A14" s="84"/>
+      <c r="B14" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="48" t="s">
+      <c r="C14" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="D14" s="48" t="s">
+      <c r="D14" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="E14" s="48" t="s">
+      <c r="E14" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="49" t="s">
+      <c r="F14" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="G14" s="48" t="s">
+      <c r="G14" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="48" t="s">
+      <c r="H14" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="I14" s="50" t="s">
+      <c r="I14" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="J14" s="51" t="s">
+      <c r="J14" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="K14" s="85" t="s">
+      <c r="K14" s="68" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="56.1" customHeight="1" thickBot="1">
-      <c r="A15" s="95" t="s">
+      <c r="A15" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="C15" s="38" t="s">
+      <c r="C15" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="40" t="s">
+      <c r="E15" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="38" t="s">
+      <c r="F15" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="G15" s="23" t="s">
+      <c r="G15" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="39" t="s">
+      <c r="H15" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="I15" s="41" t="s">
+      <c r="I15" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="J15" s="38" t="s">
+      <c r="J15" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="K15" s="36" t="s">
+      <c r="K15" s="26" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="98.1" customHeight="1">
-      <c r="A16" s="93"/>
-      <c r="B16" s="20" t="s">
+      <c r="A16" s="83"/>
+      <c r="B16" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="H16" s="31" t="s">
+      <c r="H16" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="I16" s="15" t="s">
+      <c r="I16" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="J16" s="18" t="s">
+      <c r="J16" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="K16" s="86" t="s">
+      <c r="K16" s="69" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A17" s="93"/>
-      <c r="B17" s="20" t="s">
+      <c r="A17" s="83"/>
+      <c r="B17" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="16" t="s">
+      <c r="F17" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="G17" s="16" t="s">
+      <c r="G17" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="20" t="s">
+      <c r="H17" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="I17" s="15" t="s">
+      <c r="I17" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="J17" s="18" t="s">
+      <c r="J17" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="K17" s="86" t="s">
+      <c r="K17" s="69" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A18" s="93"/>
-      <c r="B18" s="20" t="s">
+      <c r="A18" s="83"/>
+      <c r="B18" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="F18" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="G18" s="16" t="s">
+      <c r="G18" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="H18" s="31" t="s">
+      <c r="H18" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="I18" s="15" t="s">
+      <c r="I18" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="J18" s="18" t="s">
+      <c r="J18" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="K18" s="86" t="s">
+      <c r="K18" s="69" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A19" s="93"/>
-      <c r="B19" s="20" t="s">
+      <c r="A19" s="83"/>
+      <c r="B19" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="F19" s="16" t="s">
+      <c r="F19" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="G19" s="16" t="s">
+      <c r="G19" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="H19" s="31" t="s">
+      <c r="H19" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="I19" s="15" t="s">
+      <c r="I19" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="J19" s="16" t="s">
+      <c r="J19" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="K19" s="86" t="s">
+      <c r="K19" s="69" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A20" s="93"/>
-      <c r="B20" s="20" t="s">
+      <c r="A20" s="83"/>
+      <c r="B20" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="G20" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="H20" s="22" t="s">
+      <c r="H20" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="I20" s="15" t="s">
+      <c r="I20" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="J20" s="16" t="s">
+      <c r="J20" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="K20" s="86" t="s">
+      <c r="K20" s="69" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A21" s="93"/>
-      <c r="B21" s="21" t="s">
+    <row r="21" spans="1:11" ht="54.95" customHeight="1">
+      <c r="A21" s="83"/>
+      <c r="B21" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="C21" s="63" t="s">
+      <c r="C21" s="53" t="s">
         <v>138</v>
       </c>
-      <c r="D21" s="64" t="s">
+      <c r="D21" s="54" t="s">
         <v>139</v>
       </c>
-      <c r="E21" s="65" t="s">
+      <c r="E21" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="64" t="s">
+      <c r="F21" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="G21" s="64" t="s">
+      <c r="G21" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="H21" s="66" t="s">
+      <c r="H21" s="56" t="s">
         <v>139</v>
       </c>
-      <c r="I21" s="37" t="s">
+      <c r="I21" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="J21" s="64" t="s">
+      <c r="J21" s="54" t="s">
         <v>142</v>
       </c>
-      <c r="K21" s="87" t="s">
+      <c r="K21" s="70" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="98.1" customHeight="1">
-      <c r="A22" s="98" t="s">
+      <c r="A22" s="90" t="s">
+        <v>346</v>
+      </c>
+      <c r="B22" s="99" t="s">
         <v>143</v>
       </c>
-      <c r="B22" s="67" t="s">
+      <c r="C22" s="99" t="s">
+        <v>347</v>
+      </c>
+      <c r="D22" s="99" t="s">
         <v>144</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="E22" s="99" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="99" t="s">
         <v>145</v>
       </c>
-      <c r="D22" s="69" t="s">
+      <c r="G22" s="99" t="s">
         <v>146</v>
       </c>
-      <c r="E22" s="67" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="70" t="s">
+      <c r="H22" s="99" t="s">
         <v>147</v>
       </c>
-      <c r="G22" s="67" t="s">
+      <c r="I22" s="99" t="s">
         <v>148</v>
       </c>
-      <c r="H22" s="67" t="s">
+      <c r="J22" s="99" t="s">
         <v>149</v>
       </c>
-      <c r="I22" s="67" t="s">
+      <c r="K22" s="99" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="75">
+      <c r="A23" s="90"/>
+      <c r="B23" s="99" t="s">
         <v>150</v>
       </c>
-      <c r="J22" s="67" t="s">
+      <c r="C23" s="99" t="s">
+        <v>348</v>
+      </c>
+      <c r="D23" s="99" t="s">
         <v>151</v>
       </c>
-      <c r="K22" s="9" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A23" s="90"/>
-      <c r="B23" s="24" t="s">
+      <c r="E23" s="99" t="s">
         <v>152</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="F23" s="99" t="s">
+        <v>349</v>
+      </c>
+      <c r="G23" s="99" t="s">
         <v>153</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="H23" s="99" t="s">
         <v>154</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="I23" s="99" t="s">
+        <v>364</v>
+      </c>
+      <c r="J23" s="99" t="s">
         <v>155</v>
       </c>
-      <c r="F23" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="G23" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="H23" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="I23" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="J23" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="K23" s="5" t="s">
+      <c r="K23" s="99" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="69.95" customHeight="1">
       <c r="A24" s="90"/>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="99" t="s">
+        <v>156</v>
+      </c>
+      <c r="C24" s="99" t="s">
+        <v>157</v>
+      </c>
+      <c r="D24" s="99" t="s">
+        <v>158</v>
+      </c>
+      <c r="E24" s="99" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="99" t="s">
+        <v>350</v>
+      </c>
+      <c r="G24" s="99" t="s">
+        <v>159</v>
+      </c>
+      <c r="H24" s="99" t="s">
+        <v>160</v>
+      </c>
+      <c r="I24" s="99" t="s">
+        <v>365</v>
+      </c>
+      <c r="J24" s="99" t="s">
         <v>161</v>
       </c>
-      <c r="C24" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E24" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>164</v>
-      </c>
-      <c r="G24" s="24" t="s">
-        <v>165</v>
-      </c>
-      <c r="H24" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="I24" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="J24" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="K24" s="5" t="s">
+      <c r="K24" s="99" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="69.95" customHeight="1">
       <c r="A25" s="90"/>
-      <c r="B25" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="C25" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E25" s="24" t="s">
+      <c r="B25" s="99" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" s="99" t="s">
+        <v>163</v>
+      </c>
+      <c r="D25" s="99" t="s">
+        <v>164</v>
+      </c>
+      <c r="E25" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="F25" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="G25" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="H25" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="I25" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="J25" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="K25" s="5" t="s">
+      <c r="F25" s="99" t="s">
+        <v>165</v>
+      </c>
+      <c r="G25" s="99" t="s">
+        <v>166</v>
+      </c>
+      <c r="H25" s="99" t="s">
+        <v>167</v>
+      </c>
+      <c r="I25" s="99" t="s">
+        <v>366</v>
+      </c>
+      <c r="J25" s="99" t="s">
+        <v>168</v>
+      </c>
+      <c r="K25" s="99" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="84" customHeight="1">
       <c r="A26" s="90"/>
-      <c r="B26" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E26" s="24" t="s">
+      <c r="B26" s="99" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" s="99" t="s">
+        <v>170</v>
+      </c>
+      <c r="D26" s="99" t="s">
+        <v>171</v>
+      </c>
+      <c r="E26" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="F26" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="G26" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="H26" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="I26" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="J26" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="K26" s="5" t="s">
+      <c r="F26" s="99" t="s">
+        <v>172</v>
+      </c>
+      <c r="G26" s="99" t="s">
+        <v>173</v>
+      </c>
+      <c r="H26" s="99" t="s">
+        <v>174</v>
+      </c>
+      <c r="I26" s="99" t="s">
+        <v>367</v>
+      </c>
+      <c r="J26" s="99" t="s">
+        <v>175</v>
+      </c>
+      <c r="K26" s="99" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="84" customHeight="1">
       <c r="A27" s="90"/>
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="99" t="s">
+        <v>176</v>
+      </c>
+      <c r="C27" s="99" t="s">
+        <v>177</v>
+      </c>
+      <c r="D27" s="99" t="s">
+        <v>178</v>
+      </c>
+      <c r="E27" s="99" t="s">
+        <v>38</v>
+      </c>
+      <c r="F27" s="99" t="s">
+        <v>351</v>
+      </c>
+      <c r="G27" s="99" t="s">
+        <v>146</v>
+      </c>
+      <c r="H27" s="99" t="s">
+        <v>179</v>
+      </c>
+      <c r="I27" s="99" t="s">
+        <v>368</v>
+      </c>
+      <c r="J27" s="99" t="s">
+        <v>180</v>
+      </c>
+      <c r="K27" s="99" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="69.95" customHeight="1">
+      <c r="A28" s="90"/>
+      <c r="B28" s="91" t="s">
+        <v>181</v>
+      </c>
+      <c r="C28" s="91" t="s">
+        <v>182</v>
+      </c>
+      <c r="D28" s="91" t="s">
+        <v>183</v>
+      </c>
+      <c r="E28" s="91" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="G28" s="91" t="s">
         <v>185</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="H28" s="91" t="s">
         <v>186</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="I28" s="99" t="s">
+        <v>369</v>
+      </c>
+      <c r="J28" s="99" t="s">
         <v>187</v>
       </c>
-      <c r="E27" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="F27" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="G27" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="H27" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="I27" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="J27" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="69.95" customHeight="1" thickBot="1">
-      <c r="A28" s="97"/>
-      <c r="B28" s="71" t="s">
-        <v>192</v>
-      </c>
-      <c r="C28" s="71" t="s">
-        <v>193</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="F28" s="71" t="s">
-        <v>195</v>
-      </c>
-      <c r="G28" s="71" t="s">
-        <v>196</v>
-      </c>
-      <c r="H28" s="71" t="s">
-        <v>197</v>
-      </c>
-      <c r="I28" s="71" t="s">
-        <v>198</v>
-      </c>
-      <c r="J28" s="71" t="s">
-        <v>199</v>
-      </c>
-      <c r="K28" s="7" t="s">
+      <c r="K28" s="99" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="69.95" customHeight="1" thickBot="1">
-      <c r="A29" s="89" t="s">
-        <v>200</v>
-      </c>
-      <c r="B29" s="67" t="s">
-        <v>201</v>
-      </c>
-      <c r="C29" s="67" t="s">
-        <v>202</v>
-      </c>
-      <c r="D29" s="69" t="s">
-        <v>203</v>
-      </c>
-      <c r="E29" s="67" t="s">
+      <c r="A29" s="86" t="s">
+        <v>188</v>
+      </c>
+      <c r="B29" s="87" t="s">
+        <v>189</v>
+      </c>
+      <c r="C29" s="87" t="s">
+        <v>190</v>
+      </c>
+      <c r="D29" s="88" t="s">
+        <v>191</v>
+      </c>
+      <c r="E29" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="F29" s="67" t="s">
-        <v>204</v>
-      </c>
-      <c r="G29" s="67" t="s">
-        <v>148</v>
-      </c>
-      <c r="H29" s="67" t="s">
-        <v>205</v>
-      </c>
-      <c r="I29" s="67" t="s">
-        <v>206</v>
-      </c>
-      <c r="J29" s="67" t="s">
-        <v>207</v>
-      </c>
-      <c r="K29" s="9" t="s">
+      <c r="F29" s="87" t="s">
+        <v>192</v>
+      </c>
+      <c r="G29" s="87" t="s">
+        <v>146</v>
+      </c>
+      <c r="H29" s="87" t="s">
+        <v>193</v>
+      </c>
+      <c r="I29" s="87" t="s">
+        <v>194</v>
+      </c>
+      <c r="J29" s="87" t="s">
+        <v>195</v>
+      </c>
+      <c r="K29" s="89" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="84" customHeight="1">
-      <c r="A30" s="90"/>
-      <c r="B30" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="D30" s="69" t="s">
-        <v>203</v>
-      </c>
-      <c r="E30" s="24" t="s">
+      <c r="A30" s="80"/>
+      <c r="B30" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="D30" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="E30" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="F30" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="G30" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="H30" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="I30" s="24" t="s">
-        <v>212</v>
-      </c>
-      <c r="J30" s="24" t="s">
-        <v>213</v>
+      <c r="F30" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="G30" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="H30" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="I30" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="J30" s="21" t="s">
+        <v>201</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A31" s="90"/>
-      <c r="B31" s="24" t="s">
-        <v>214</v>
-      </c>
-      <c r="C31" s="24" t="s">
-        <v>215</v>
+      <c r="A31" s="80"/>
+      <c r="B31" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>203</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="E31" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="E31" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="F31" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="G31" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="H31" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="I31" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="J31" s="24" t="s">
-        <v>220</v>
+      <c r="F31" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="H31" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="I31" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="J31" s="21" t="s">
+        <v>208</v>
       </c>
       <c r="K31" s="5" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A32" s="91"/>
-      <c r="B32" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="E32" s="11" t="s">
+      <c r="A32" s="81"/>
+      <c r="B32" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E32" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F32" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="G32" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="H32" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="I32" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="J32" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="K32" s="13" t="s">
+      <c r="F32" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="K32" s="11" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="98.1" customHeight="1">
-      <c r="A33" s="99" t="s">
-        <v>229</v>
-      </c>
-      <c r="B33" s="72" t="s">
-        <v>230</v>
-      </c>
-      <c r="C33" s="72" t="s">
-        <v>231</v>
-      </c>
-      <c r="D33" s="73" t="s">
-        <v>232</v>
-      </c>
-      <c r="E33" s="72" t="s">
+      <c r="A33" s="77" t="s">
+        <v>217</v>
+      </c>
+      <c r="B33" s="58" t="s">
+        <v>218</v>
+      </c>
+      <c r="C33" s="58" t="s">
+        <v>219</v>
+      </c>
+      <c r="D33" s="59" t="s">
+        <v>220</v>
+      </c>
+      <c r="E33" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="F33" s="72" t="s">
-        <v>233</v>
-      </c>
-      <c r="G33" s="72" t="s">
-        <v>234</v>
-      </c>
-      <c r="H33" s="72" t="s">
-        <v>235</v>
-      </c>
-      <c r="I33" s="72" t="s">
-        <v>236</v>
-      </c>
-      <c r="J33" s="72" t="s">
-        <v>237</v>
-      </c>
-      <c r="K33" s="74" t="s">
+      <c r="F33" s="58" t="s">
+        <v>221</v>
+      </c>
+      <c r="G33" s="58" t="s">
+        <v>222</v>
+      </c>
+      <c r="H33" s="58" t="s">
+        <v>223</v>
+      </c>
+      <c r="I33" s="58" t="s">
+        <v>224</v>
+      </c>
+      <c r="J33" s="58" t="s">
+        <v>225</v>
+      </c>
+      <c r="K33" s="60" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="98.1" customHeight="1" thickBot="1">
-      <c r="A34" s="97"/>
-      <c r="B34" s="75" t="s">
+      <c r="A34" s="78"/>
+      <c r="B34" s="61" t="s">
+        <v>226</v>
+      </c>
+      <c r="C34" s="61" t="s">
+        <v>227</v>
+      </c>
+      <c r="D34" s="62" t="s">
+        <v>220</v>
+      </c>
+      <c r="E34" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" s="61" t="s">
+        <v>228</v>
+      </c>
+      <c r="G34" s="61" t="s">
+        <v>229</v>
+      </c>
+      <c r="H34" s="61" t="s">
+        <v>230</v>
+      </c>
+      <c r="I34" s="61" t="s">
+        <v>231</v>
+      </c>
+      <c r="J34" s="61" t="s">
+        <v>232</v>
+      </c>
+      <c r="K34" s="63" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="69.95" customHeight="1" thickBot="1">
+      <c r="A35" s="77" t="s">
+        <v>233</v>
+      </c>
+      <c r="B35" s="58" t="s">
+        <v>234</v>
+      </c>
+      <c r="C35" s="58" t="s">
+        <v>235</v>
+      </c>
+      <c r="D35" s="59" t="s">
+        <v>236</v>
+      </c>
+      <c r="E35" s="58" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="58" t="s">
+        <v>237</v>
+      </c>
+      <c r="G35" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35" s="58" t="s">
+        <v>236</v>
+      </c>
+      <c r="I35" s="58" t="s">
         <v>238</v>
       </c>
-      <c r="C34" s="75" t="s">
+      <c r="J35" s="58" t="s">
         <v>239</v>
       </c>
-      <c r="D34" s="76" t="s">
-        <v>232</v>
-      </c>
-      <c r="E34" s="75" t="s">
-        <v>16</v>
-      </c>
-      <c r="F34" s="75" t="s">
-        <v>240</v>
-      </c>
-      <c r="G34" s="75" t="s">
-        <v>241</v>
-      </c>
-      <c r="H34" s="75" t="s">
-        <v>242</v>
-      </c>
-      <c r="I34" s="75" t="s">
-        <v>243</v>
-      </c>
-      <c r="J34" s="75" t="s">
-        <v>244</v>
-      </c>
-      <c r="K34" s="77" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A35" s="99" t="s">
-        <v>245</v>
-      </c>
-      <c r="B35" s="72" t="s">
-        <v>246</v>
-      </c>
-      <c r="C35" s="72" t="s">
-        <v>247</v>
-      </c>
-      <c r="D35" s="73" t="s">
-        <v>248</v>
-      </c>
-      <c r="E35" s="72" t="s">
-        <v>16</v>
-      </c>
-      <c r="F35" s="72" t="s">
-        <v>249</v>
-      </c>
-      <c r="G35" s="72" t="s">
-        <v>18</v>
-      </c>
-      <c r="H35" s="72" t="s">
-        <v>248</v>
-      </c>
-      <c r="I35" s="72" t="s">
-        <v>250</v>
-      </c>
-      <c r="J35" s="72" t="s">
-        <v>251</v>
-      </c>
-      <c r="K35" s="74" t="s">
+      <c r="K35" s="60" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A36" s="90"/>
-      <c r="B36" s="78" t="s">
-        <v>252</v>
-      </c>
-      <c r="C36" s="78" t="s">
-        <v>253</v>
-      </c>
-      <c r="D36" s="79" t="s">
-        <v>254</v>
-      </c>
-      <c r="E36" s="78" t="s">
+      <c r="A36" s="80"/>
+      <c r="B36" s="64" t="s">
+        <v>240</v>
+      </c>
+      <c r="C36" s="64" t="s">
+        <v>241</v>
+      </c>
+      <c r="D36" s="65" t="s">
+        <v>242</v>
+      </c>
+      <c r="E36" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="F36" s="78" t="s">
-        <v>255</v>
-      </c>
-      <c r="G36" s="78" t="s">
+      <c r="F36" s="64" t="s">
+        <v>243</v>
+      </c>
+      <c r="G36" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="H36" s="78" t="s">
-        <v>254</v>
-      </c>
-      <c r="I36" s="78" t="s">
-        <v>256</v>
-      </c>
-      <c r="J36" s="78" t="s">
-        <v>257</v>
-      </c>
-      <c r="K36" s="81" t="s">
+      <c r="H36" s="64" t="s">
+        <v>242</v>
+      </c>
+      <c r="I36" s="64" t="s">
+        <v>244</v>
+      </c>
+      <c r="J36" s="64" t="s">
+        <v>245</v>
+      </c>
+      <c r="K36" s="66" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="84" customHeight="1">
-      <c r="A37" s="90"/>
-      <c r="B37" s="78" t="s">
-        <v>258</v>
-      </c>
-      <c r="C37" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="D37" s="79" t="s">
-        <v>254</v>
-      </c>
-      <c r="E37" s="78" t="s">
+      <c r="A37" s="80"/>
+      <c r="B37" s="64" t="s">
+        <v>246</v>
+      </c>
+      <c r="C37" s="64" t="s">
+        <v>247</v>
+      </c>
+      <c r="D37" s="65" t="s">
+        <v>242</v>
+      </c>
+      <c r="E37" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="F37" s="78" t="s">
-        <v>260</v>
-      </c>
-      <c r="G37" s="78" t="s">
-        <v>261</v>
-      </c>
-      <c r="H37" s="78" t="s">
-        <v>262</v>
-      </c>
-      <c r="I37" s="78" t="s">
-        <v>263</v>
-      </c>
-      <c r="J37" s="78" t="s">
-        <v>264</v>
-      </c>
-      <c r="K37" s="81" t="s">
+      <c r="F37" s="64" t="s">
+        <v>248</v>
+      </c>
+      <c r="G37" s="64" t="s">
+        <v>249</v>
+      </c>
+      <c r="H37" s="64" t="s">
+        <v>250</v>
+      </c>
+      <c r="I37" s="64" t="s">
+        <v>251</v>
+      </c>
+      <c r="J37" s="64" t="s">
+        <v>252</v>
+      </c>
+      <c r="K37" s="66" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A38" s="90"/>
-      <c r="B38" s="78" t="s">
-        <v>265</v>
-      </c>
-      <c r="C38" s="78" t="s">
-        <v>266</v>
-      </c>
-      <c r="D38" s="79" t="s">
-        <v>267</v>
-      </c>
-      <c r="E38" s="78" t="s">
+      <c r="A38" s="80"/>
+      <c r="B38" s="64" t="s">
+        <v>253</v>
+      </c>
+      <c r="C38" s="64" t="s">
+        <v>254</v>
+      </c>
+      <c r="D38" s="65" t="s">
+        <v>255</v>
+      </c>
+      <c r="E38" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="F38" s="78" t="s">
-        <v>268</v>
-      </c>
-      <c r="G38" s="78" t="s">
+      <c r="F38" s="64" t="s">
+        <v>256</v>
+      </c>
+      <c r="G38" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="H38" s="78" t="s">
-        <v>267</v>
-      </c>
-      <c r="I38" s="78" t="s">
-        <v>269</v>
-      </c>
-      <c r="J38" s="78" t="s">
-        <v>270</v>
-      </c>
-      <c r="K38" s="81" t="s">
+      <c r="H38" s="64" t="s">
+        <v>255</v>
+      </c>
+      <c r="I38" s="64" t="s">
+        <v>257</v>
+      </c>
+      <c r="J38" s="64" t="s">
+        <v>258</v>
+      </c>
+      <c r="K38" s="66" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="84" customHeight="1">
-      <c r="A39" s="90"/>
-      <c r="B39" s="78" t="s">
-        <v>271</v>
-      </c>
-      <c r="C39" s="78" t="s">
-        <v>272</v>
-      </c>
-      <c r="D39" s="79" t="s">
-        <v>273</v>
-      </c>
-      <c r="E39" s="78" t="s">
+      <c r="A39" s="80"/>
+      <c r="B39" s="64" t="s">
+        <v>259</v>
+      </c>
+      <c r="C39" s="64" t="s">
+        <v>260</v>
+      </c>
+      <c r="D39" s="65" t="s">
+        <v>261</v>
+      </c>
+      <c r="E39" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="F39" s="78" t="s">
-        <v>274</v>
-      </c>
-      <c r="G39" s="78" t="s">
-        <v>275</v>
-      </c>
-      <c r="H39" s="78" t="s">
-        <v>276</v>
-      </c>
-      <c r="I39" s="78" t="s">
-        <v>277</v>
-      </c>
-      <c r="J39" s="78" t="s">
-        <v>278</v>
-      </c>
-      <c r="K39" s="81" t="s">
+      <c r="F39" s="64" t="s">
+        <v>262</v>
+      </c>
+      <c r="G39" s="64" t="s">
+        <v>263</v>
+      </c>
+      <c r="H39" s="64" t="s">
+        <v>264</v>
+      </c>
+      <c r="I39" s="64" t="s">
+        <v>265</v>
+      </c>
+      <c r="J39" s="64" t="s">
+        <v>266</v>
+      </c>
+      <c r="K39" s="66" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="84" customHeight="1">
-      <c r="A40" s="90"/>
-      <c r="B40" s="78" t="s">
-        <v>279</v>
-      </c>
-      <c r="C40" s="78" t="s">
-        <v>280</v>
-      </c>
-      <c r="D40" s="79" t="s">
-        <v>281</v>
-      </c>
-      <c r="E40" s="78" t="s">
+      <c r="A40" s="80"/>
+      <c r="B40" s="64" t="s">
+        <v>267</v>
+      </c>
+      <c r="C40" s="64" t="s">
+        <v>268</v>
+      </c>
+      <c r="D40" s="65" t="s">
+        <v>269</v>
+      </c>
+      <c r="E40" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="F40" s="78" t="s">
-        <v>282</v>
-      </c>
-      <c r="G40" s="78" t="s">
-        <v>283</v>
-      </c>
-      <c r="H40" s="78" t="s">
-        <v>284</v>
-      </c>
-      <c r="I40" s="78" t="s">
-        <v>277</v>
-      </c>
-      <c r="J40" s="78" t="s">
-        <v>285</v>
-      </c>
-      <c r="K40" s="81" t="s">
+      <c r="F40" s="64" t="s">
+        <v>270</v>
+      </c>
+      <c r="G40" s="64" t="s">
+        <v>271</v>
+      </c>
+      <c r="H40" s="64" t="s">
+        <v>272</v>
+      </c>
+      <c r="I40" s="64" t="s">
+        <v>265</v>
+      </c>
+      <c r="J40" s="64" t="s">
+        <v>273</v>
+      </c>
+      <c r="K40" s="66" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="54.95" customHeight="1">
-      <c r="A41" s="90"/>
-      <c r="B41" s="78" t="s">
-        <v>286</v>
-      </c>
-      <c r="C41" s="78" t="s">
-        <v>287</v>
-      </c>
-      <c r="D41" s="79" t="s">
-        <v>288</v>
-      </c>
-      <c r="E41" s="78" t="s">
+      <c r="A41" s="80"/>
+      <c r="B41" s="64" t="s">
+        <v>274</v>
+      </c>
+      <c r="C41" s="64" t="s">
+        <v>275</v>
+      </c>
+      <c r="D41" s="65" t="s">
+        <v>276</v>
+      </c>
+      <c r="E41" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="F41" s="78" t="s">
-        <v>289</v>
-      </c>
-      <c r="G41" s="78" t="s">
-        <v>148</v>
-      </c>
-      <c r="H41" s="78" t="s">
-        <v>189</v>
-      </c>
-      <c r="I41" s="78" t="s">
-        <v>290</v>
-      </c>
-      <c r="J41" s="78" t="s">
-        <v>291</v>
-      </c>
-      <c r="K41" s="81" t="s">
+      <c r="F41" s="64" t="s">
+        <v>277</v>
+      </c>
+      <c r="G41" s="64" t="s">
+        <v>146</v>
+      </c>
+      <c r="H41" s="64" t="s">
+        <v>179</v>
+      </c>
+      <c r="I41" s="64" t="s">
+        <v>278</v>
+      </c>
+      <c r="J41" s="64" t="s">
+        <v>279</v>
+      </c>
+      <c r="K41" s="66" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="84" customHeight="1">
-      <c r="A42" s="90"/>
-      <c r="B42" s="78" t="s">
-        <v>292</v>
-      </c>
-      <c r="C42" s="78" t="s">
-        <v>293</v>
-      </c>
-      <c r="D42" s="79" t="s">
-        <v>294</v>
-      </c>
-      <c r="E42" s="78" t="s">
+      <c r="A42" s="80"/>
+      <c r="B42" s="64" t="s">
+        <v>280</v>
+      </c>
+      <c r="C42" s="64" t="s">
+        <v>281</v>
+      </c>
+      <c r="D42" s="65" t="s">
+        <v>282</v>
+      </c>
+      <c r="E42" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="F42" s="78" t="s">
-        <v>295</v>
-      </c>
-      <c r="G42" s="78" t="s">
+      <c r="F42" s="64" t="s">
+        <v>283</v>
+      </c>
+      <c r="G42" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="H42" s="78" t="s">
-        <v>294</v>
-      </c>
-      <c r="I42" s="78" t="s">
-        <v>296</v>
-      </c>
-      <c r="J42" s="78" t="s">
-        <v>297</v>
-      </c>
-      <c r="K42" s="81" t="s">
+      <c r="H42" s="64" t="s">
+        <v>282</v>
+      </c>
+      <c r="I42" s="64" t="s">
+        <v>284</v>
+      </c>
+      <c r="J42" s="64" t="s">
+        <v>285</v>
+      </c>
+      <c r="K42" s="66" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="54.95" customHeight="1">
-      <c r="A43" s="90"/>
-      <c r="B43" s="78" t="s">
-        <v>298</v>
-      </c>
-      <c r="C43" s="78" t="s">
-        <v>299</v>
-      </c>
-      <c r="D43" s="79" t="s">
-        <v>300</v>
-      </c>
-      <c r="E43" s="78" t="s">
+      <c r="A43" s="80"/>
+      <c r="B43" s="64" t="s">
+        <v>286</v>
+      </c>
+      <c r="C43" s="64" t="s">
+        <v>287</v>
+      </c>
+      <c r="D43" s="65" t="s">
+        <v>288</v>
+      </c>
+      <c r="E43" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="F43" s="78" t="s">
-        <v>301</v>
-      </c>
-      <c r="G43" s="78" t="s">
-        <v>302</v>
-      </c>
-      <c r="H43" s="78" t="s">
-        <v>303</v>
-      </c>
-      <c r="I43" s="78" t="s">
-        <v>304</v>
-      </c>
-      <c r="J43" s="78" t="s">
-        <v>305</v>
-      </c>
-      <c r="K43" s="81" t="s">
+      <c r="F43" s="64" t="s">
+        <v>289</v>
+      </c>
+      <c r="G43" s="64" t="s">
+        <v>290</v>
+      </c>
+      <c r="H43" s="64" t="s">
+        <v>291</v>
+      </c>
+      <c r="I43" s="64" t="s">
+        <v>292</v>
+      </c>
+      <c r="J43" s="64" t="s">
+        <v>293</v>
+      </c>
+      <c r="K43" s="66" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="67.5" customHeight="1" thickBot="1">
-      <c r="A44" s="97"/>
-      <c r="B44" s="80" t="s">
-        <v>306</v>
-      </c>
-      <c r="C44" s="80" t="s">
-        <v>307</v>
-      </c>
-      <c r="D44" s="82" t="s">
-        <v>308</v>
-      </c>
-      <c r="E44" s="80" t="s">
+      <c r="A44" s="78"/>
+      <c r="B44" s="93" t="s">
+        <v>294</v>
+      </c>
+      <c r="C44" s="93" t="s">
+        <v>295</v>
+      </c>
+      <c r="D44" s="94" t="s">
+        <v>296</v>
+      </c>
+      <c r="E44" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="F44" s="80" t="s">
-        <v>301</v>
-      </c>
-      <c r="G44" s="80" t="s">
-        <v>309</v>
-      </c>
-      <c r="H44" s="80" t="s">
-        <v>310</v>
-      </c>
-      <c r="I44" s="80" t="s">
-        <v>304</v>
-      </c>
-      <c r="J44" s="80" t="s">
-        <v>311</v>
-      </c>
-      <c r="K44" s="83" t="s">
+      <c r="F44" s="93" t="s">
+        <v>289</v>
+      </c>
+      <c r="G44" s="93" t="s">
+        <v>297</v>
+      </c>
+      <c r="H44" s="93" t="s">
+        <v>298</v>
+      </c>
+      <c r="I44" s="93" t="s">
+        <v>292</v>
+      </c>
+      <c r="J44" s="93" t="s">
+        <v>299</v>
+      </c>
+      <c r="K44" s="95" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="84" customHeight="1">
-      <c r="A45" s="96" t="s">
-        <v>312</v>
-      </c>
-      <c r="B45" s="67" t="s">
-        <v>313</v>
-      </c>
-      <c r="C45" s="67" t="s">
-        <v>314</v>
-      </c>
-      <c r="D45" s="69" t="s">
-        <v>315</v>
-      </c>
-      <c r="E45" s="67" t="s">
+      <c r="A45" s="92" t="s">
+        <v>352</v>
+      </c>
+      <c r="B45" s="99" t="s">
+        <v>300</v>
+      </c>
+      <c r="C45" s="99" t="s">
+        <v>301</v>
+      </c>
+      <c r="D45" s="99" t="s">
+        <v>302</v>
+      </c>
+      <c r="E45" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="F45" s="68" t="s">
-        <v>316</v>
-      </c>
-      <c r="G45" s="67" t="s">
-        <v>317</v>
-      </c>
-      <c r="H45" s="67" t="s">
-        <v>318</v>
-      </c>
-      <c r="I45" s="67" t="s">
-        <v>319</v>
-      </c>
-      <c r="J45" s="67" t="s">
-        <v>320</v>
-      </c>
-      <c r="K45" s="27" t="s">
-        <v>321</v>
+      <c r="F45" s="99" t="s">
+        <v>353</v>
+      </c>
+      <c r="G45" s="99" t="s">
+        <v>303</v>
+      </c>
+      <c r="H45" s="99" t="s">
+        <v>304</v>
+      </c>
+      <c r="I45" s="99" t="s">
+        <v>305</v>
+      </c>
+      <c r="J45" s="99" t="s">
+        <v>306</v>
+      </c>
+      <c r="K45" s="99" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="84" customHeight="1">
-      <c r="A46" s="90"/>
-      <c r="B46" s="24" t="s">
-        <v>322</v>
-      </c>
-      <c r="C46" s="25" t="s">
-        <v>323</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="E46" s="24" t="s">
+      <c r="A46" s="92"/>
+      <c r="B46" s="99" t="s">
+        <v>308</v>
+      </c>
+      <c r="C46" s="99" t="s">
+        <v>355</v>
+      </c>
+      <c r="D46" s="99" t="s">
+        <v>309</v>
+      </c>
+      <c r="E46" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="F46" s="25" t="s">
-        <v>325</v>
-      </c>
-      <c r="G46" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="H46" s="24" t="s">
-        <v>326</v>
-      </c>
-      <c r="I46" s="24" t="s">
-        <v>327</v>
-      </c>
-      <c r="J46" s="24" t="s">
-        <v>328</v>
-      </c>
-      <c r="K46" s="28" t="s">
-        <v>321</v>
+      <c r="F46" s="99" t="s">
+        <v>356</v>
+      </c>
+      <c r="G46" s="99" t="s">
+        <v>146</v>
+      </c>
+      <c r="H46" s="99" t="s">
+        <v>310</v>
+      </c>
+      <c r="I46" s="99" t="s">
+        <v>377</v>
+      </c>
+      <c r="J46" s="99" t="s">
+        <v>311</v>
+      </c>
+      <c r="K46" s="99" t="s">
+        <v>354</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="84" customHeight="1">
-      <c r="A47" s="90"/>
-      <c r="B47" s="24" t="s">
-        <v>329</v>
-      </c>
-      <c r="C47" s="25" t="s">
-        <v>330</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="E47" s="25" t="s">
+    <row r="47" spans="1:11" ht="97.5">
+      <c r="A47" s="92"/>
+      <c r="B47" s="99" t="s">
+        <v>312</v>
+      </c>
+      <c r="C47" s="99" t="s">
+        <v>357</v>
+      </c>
+      <c r="D47" s="99" t="s">
+        <v>313</v>
+      </c>
+      <c r="E47" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="F47" s="25" t="s">
-        <v>332</v>
-      </c>
-      <c r="G47" s="24" t="s">
-        <v>333</v>
-      </c>
-      <c r="H47" s="24" t="s">
-        <v>334</v>
-      </c>
-      <c r="I47" s="24" t="s">
-        <v>335</v>
-      </c>
-      <c r="J47" s="24" t="s">
-        <v>336</v>
-      </c>
-      <c r="K47" s="28" t="s">
-        <v>321</v>
+      <c r="F47" s="99" t="s">
+        <v>358</v>
+      </c>
+      <c r="G47" s="99" t="s">
+        <v>374</v>
+      </c>
+      <c r="H47" s="99" t="s">
+        <v>378</v>
+      </c>
+      <c r="I47" s="99" t="s">
+        <v>380</v>
+      </c>
+      <c r="J47" s="100" t="s">
+        <v>379</v>
+      </c>
+      <c r="K47" s="99" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="54.95" customHeight="1">
-      <c r="A48" s="90"/>
-      <c r="B48" s="24" t="s">
-        <v>337</v>
-      </c>
-      <c r="C48" s="25" t="s">
-        <v>338</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="E48" s="25" t="s">
+      <c r="A48" s="92"/>
+      <c r="B48" s="99" t="s">
+        <v>314</v>
+      </c>
+      <c r="C48" s="99" t="s">
+        <v>359</v>
+      </c>
+      <c r="D48" s="99" t="s">
+        <v>315</v>
+      </c>
+      <c r="E48" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="F48" s="25" t="s">
-        <v>340</v>
-      </c>
-      <c r="G48" s="24" t="s">
-        <v>341</v>
-      </c>
-      <c r="H48" s="24" t="s">
-        <v>342</v>
-      </c>
-      <c r="I48" s="24" t="s">
-        <v>343</v>
-      </c>
-      <c r="J48" s="24" t="s">
-        <v>344</v>
-      </c>
-      <c r="K48" s="28" t="s">
-        <v>321</v>
+      <c r="F48" s="99" t="s">
+        <v>360</v>
+      </c>
+      <c r="G48" s="99" t="s">
+        <v>376</v>
+      </c>
+      <c r="H48" s="99" t="s">
+        <v>381</v>
+      </c>
+      <c r="I48" s="99" t="s">
+        <v>317</v>
+      </c>
+      <c r="J48" s="99" t="s">
+        <v>318</v>
+      </c>
+      <c r="K48" s="99" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="84" customHeight="1">
-      <c r="A49" s="90"/>
-      <c r="B49" s="24" t="s">
-        <v>345</v>
-      </c>
-      <c r="C49" s="24" t="s">
-        <v>346</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="E49" s="24" t="s">
+      <c r="A49" s="92"/>
+      <c r="B49" s="99" t="s">
+        <v>319</v>
+      </c>
+      <c r="C49" s="99" t="s">
+        <v>320</v>
+      </c>
+      <c r="D49" s="99" t="s">
+        <v>321</v>
+      </c>
+      <c r="E49" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="F49" s="25" t="s">
-        <v>348</v>
-      </c>
-      <c r="G49" s="24" t="s">
-        <v>333</v>
-      </c>
-      <c r="H49" s="24" t="s">
-        <v>334</v>
-      </c>
-      <c r="I49" s="24" t="s">
-        <v>349</v>
-      </c>
-      <c r="J49" s="24" t="s">
-        <v>350</v>
-      </c>
-      <c r="K49" s="5" t="s">
-        <v>321</v>
+      <c r="F49" s="99" t="s">
+        <v>361</v>
+      </c>
+      <c r="G49" s="99" t="s">
+        <v>382</v>
+      </c>
+      <c r="H49" s="99" t="s">
+        <v>383</v>
+      </c>
+      <c r="I49" s="99" t="s">
+        <v>372</v>
+      </c>
+      <c r="J49" s="99" t="s">
+        <v>373</v>
+      </c>
+      <c r="K49" s="99" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="84" customHeight="1">
-      <c r="A50" s="90"/>
-      <c r="B50" s="24" t="s">
-        <v>351</v>
-      </c>
-      <c r="C50" s="24" t="s">
-        <v>352</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="E50" s="24" t="s">
+      <c r="A50" s="92"/>
+      <c r="B50" s="99" t="s">
+        <v>322</v>
+      </c>
+      <c r="C50" s="99" t="s">
+        <v>323</v>
+      </c>
+      <c r="D50" s="99" t="s">
+        <v>324</v>
+      </c>
+      <c r="E50" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="F50" s="25" t="s">
+      <c r="F50" s="99" t="s">
+        <v>362</v>
+      </c>
+      <c r="G50" s="99" t="s">
+        <v>316</v>
+      </c>
+      <c r="H50" s="99" t="s">
+        <v>325</v>
+      </c>
+      <c r="I50" s="99" t="s">
+        <v>326</v>
+      </c>
+      <c r="J50" s="99" t="s">
+        <v>327</v>
+      </c>
+      <c r="K50" s="99" t="s">
         <v>354</v>
-      </c>
-      <c r="G50" s="26" t="s">
-        <v>341</v>
-      </c>
-      <c r="H50" s="24" t="s">
-        <v>355</v>
-      </c>
-      <c r="I50" s="24" t="s">
-        <v>356</v>
-      </c>
-      <c r="J50" s="24" t="s">
-        <v>357</v>
-      </c>
-      <c r="K50" s="28" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A51" s="97"/>
-      <c r="B51" s="71" t="s">
-        <v>358</v>
-      </c>
-      <c r="C51" s="71" t="s">
-        <v>359</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="E51" s="71" t="s">
+      <c r="A51" s="92"/>
+      <c r="B51" s="99" t="s">
+        <v>328</v>
+      </c>
+      <c r="C51" s="99" t="s">
+        <v>329</v>
+      </c>
+      <c r="D51" s="99" t="s">
+        <v>330</v>
+      </c>
+      <c r="E51" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="F51" s="29" t="s">
-        <v>361</v>
-      </c>
-      <c r="G51" s="71" t="s">
-        <v>362</v>
-      </c>
-      <c r="H51" s="71" t="s">
+      <c r="F51" s="99" t="s">
         <v>363</v>
       </c>
-      <c r="I51" s="71" t="s">
-        <v>364</v>
-      </c>
-      <c r="J51" s="71" t="s">
-        <v>365</v>
-      </c>
-      <c r="K51" s="30" t="s">
-        <v>321</v>
+      <c r="G51" s="99" t="s">
+        <v>375</v>
+      </c>
+      <c r="H51" s="99" t="s">
+        <v>331</v>
+      </c>
+      <c r="I51" s="99" t="s">
+        <v>370</v>
+      </c>
+      <c r="J51" s="99" t="s">
+        <v>371</v>
+      </c>
+      <c r="K51" s="99" t="s">
+        <v>354</v>
       </c>
     </row>
-    <row r="52" spans="1:11" s="10" customFormat="1" ht="69.95" customHeight="1">
-      <c r="A52" s="99" t="s">
-        <v>366</v>
-      </c>
-      <c r="B52" s="72" t="s">
-        <v>367</v>
-      </c>
-      <c r="C52" s="72" t="s">
-        <v>368</v>
-      </c>
-      <c r="D52" s="73" t="s">
-        <v>369</v>
-      </c>
-      <c r="E52" s="72" t="s">
+    <row r="52" spans="1:11" s="8" customFormat="1" ht="69.95" customHeight="1" thickBot="1">
+      <c r="A52" s="77" t="s">
+        <v>332</v>
+      </c>
+      <c r="B52" s="96" t="s">
+        <v>333</v>
+      </c>
+      <c r="C52" s="96" t="s">
+        <v>334</v>
+      </c>
+      <c r="D52" s="97" t="s">
+        <v>335</v>
+      </c>
+      <c r="E52" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="F52" s="72" t="s">
-        <v>370</v>
-      </c>
-      <c r="G52" s="72" t="s">
-        <v>148</v>
-      </c>
-      <c r="H52" s="72" t="s">
-        <v>371</v>
-      </c>
-      <c r="I52" s="72" t="s">
-        <v>372</v>
-      </c>
-      <c r="J52" s="72" t="s">
-        <v>373</v>
-      </c>
-      <c r="K52" s="74" t="s">
-        <v>321</v>
+      <c r="F52" s="96" t="s">
+        <v>336</v>
+      </c>
+      <c r="G52" s="96" t="s">
+        <v>146</v>
+      </c>
+      <c r="H52" s="96" t="s">
+        <v>337</v>
+      </c>
+      <c r="I52" s="96" t="s">
+        <v>338</v>
+      </c>
+      <c r="J52" s="96" t="s">
+        <v>339</v>
+      </c>
+      <c r="K52" s="98" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="56.1" customHeight="1" thickBot="1">
-      <c r="A53" s="97"/>
-      <c r="B53" s="75" t="s">
-        <v>374</v>
-      </c>
-      <c r="C53" s="75" t="s">
-        <v>375</v>
-      </c>
-      <c r="D53" s="76" t="s">
-        <v>376</v>
-      </c>
-      <c r="E53" s="75" t="s">
+      <c r="A53" s="78"/>
+      <c r="B53" s="61" t="s">
+        <v>340</v>
+      </c>
+      <c r="C53" s="61" t="s">
+        <v>341</v>
+      </c>
+      <c r="D53" s="62" t="s">
+        <v>342</v>
+      </c>
+      <c r="E53" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="F53" s="75" t="s">
-        <v>377</v>
-      </c>
-      <c r="G53" s="75" t="s">
-        <v>148</v>
-      </c>
-      <c r="H53" s="75" t="s">
-        <v>189</v>
-      </c>
-      <c r="I53" s="75" t="s">
-        <v>378</v>
-      </c>
-      <c r="J53" s="75" t="s">
-        <v>379</v>
-      </c>
-      <c r="K53" s="77" t="s">
-        <v>321</v>
+      <c r="F53" s="61" t="s">
+        <v>343</v>
+      </c>
+      <c r="G53" s="61" t="s">
+        <v>146</v>
+      </c>
+      <c r="H53" s="61" t="s">
+        <v>179</v>
+      </c>
+      <c r="I53" s="61" t="s">
+        <v>344</v>
+      </c>
+      <c r="J53" s="61" t="s">
+        <v>345</v>
+      </c>
+      <c r="K53" s="63" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="75.75" customHeight="1">
-      <c r="A54" s="88"/>
+      <c r="A54" s="79"/>
     </row>
     <row r="55" spans="1:11" ht="54.95" customHeight="1">
-      <c r="A55" s="88"/>
+      <c r="A55" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -4414,5 +7036,6 @@
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/ClassMaterial/1차 프로젝트/6. API설계/6._API설계(김현규)ver-2.1.xlsx
+++ b/ClassMaterial/1차 프로젝트/6. API설계/6._API설계(김현규)ver-2.1.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KHK\JavaClass\ClassMaterial\1차 프로젝트\6. API설계\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D1A695-F6A2-417A-B9E4-995989981155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,12 +19,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>HyunKyu KIM</author>
   </authors>
   <commentList>
-    <comment ref="I23" authorId="0" shapeId="0" xr:uid="{BE11AFF7-CAA1-483B-AC33-557950AD60D6}">
+    <comment ref="I23" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -72,7 +71,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I24" authorId="0" shapeId="0" xr:uid="{2C52E905-7342-48B5-B804-7FD91F4C4252}">
+    <comment ref="I24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -118,7 +117,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I25" authorId="0" shapeId="0" xr:uid="{8BE1ED1B-E67C-4A33-A4F2-43FB3D7F0932}">
+    <comment ref="I25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -164,7 +163,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I26" authorId="0" shapeId="0" xr:uid="{ABB05FE7-C645-4799-85EF-F02A8AD658DE}">
+    <comment ref="I26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -211,7 +210,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I27" authorId="0" shapeId="0" xr:uid="{BBC9EDCD-9436-42AE-8655-242ECD6E0435}">
+    <comment ref="I27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -258,7 +257,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I28" authorId="0" shapeId="0" xr:uid="{B0688690-4D9F-4D60-9827-2BF306ECDB6B}">
+    <comment ref="I28" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -304,7 +303,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I49" authorId="0" shapeId="0" xr:uid="{A1E0D86B-9428-43BE-8DEE-7962E189DA2D}">
+    <comment ref="I49" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -350,7 +349,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J49" authorId="0" shapeId="0" xr:uid="{FE4A5F91-1A65-4919-BAC9-C4AD7544B5E5}">
+    <comment ref="J49" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -401,7 +400,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="385">
   <si>
     <t>API 설계</t>
   </si>
@@ -950,22 +949,6 @@
     <t>/dashboard?petId=1</t>
   </si>
   <si>
-    <t>dashboard.html
-(model: selectedPet,
-envData,
-riskLevel,
-latestAlerts,
-deviceState)</t>
-  </si>
-  <si>
-    <t>dashboard.html
-(model: {selectedPet:{petId:1,name:'보리'},
-envData:{temperature:24.3,humidity:51},
-riskLevel:'주의',
-latestAlerts:[2],
-deviceState:{camera:'ON', feeder:'READY'}})</t>
-  </si>
-  <si>
     <t>dash-002</t>
   </si>
   <si>
@@ -996,9 +979,6 @@
     <t>/dashboard/night-mode</t>
   </si>
   <si>
-    <t>petId, enabled</t>
-  </si>
-  <si>
     <t>petId=1&amp;enabled=true</t>
   </si>
   <si>
@@ -1038,42 +1018,16 @@
     <t>원격 사료 급여 제어</t>
   </si>
   <si>
-    <t>/dashboard/feed</t>
-  </si>
-  <si>
     <t>사료 급여 버튼 클릭 시 나타나는 모달창에서 선택한 반려동물에게 지정된 양의 사료를 제공한다.</t>
   </si>
   <si>
-    <t>petId, amount</t>
-  </si>
-  <si>
-    <t>petId=1&amp;amount=30</t>
-  </si>
-  <si>
-    <t>dashboard.html
-(model: {petId:1,
-feedResult:'SUCCESS',
-lastFeedAt:'2026-03-27 14:10:00',
-message:'30g 급여를 완료했습니다.'})</t>
-  </si>
-  <si>
     <t>dash-006</t>
   </si>
   <si>
     <t>스냅샷 캡처</t>
   </si>
   <si>
-    <t>/dashboard/capture</t>
-  </si>
-  <si>
     <t>petId=1</t>
-  </si>
-  <si>
-    <t>dashboard.html
-(model: {petId:1,
-capturedMediaId:101,
-thumbnailUrl:'/images/capture101.jpg',
-message:'스냅샷이 저장되었습니다.'})</t>
   </si>
   <si>
     <t>dash-007</t>
@@ -1546,9 +1500,6 @@
     <t>관리자</t>
   </si>
   <si>
-    <t>admin-002</t>
-  </si>
-  <si>
     <t>/admin/pets/{petId}</t>
   </si>
   <si>
@@ -1573,9 +1524,6 @@
     <t>/admin/pets/{petId}/delete</t>
   </si>
   <si>
-    <t>logId</t>
-  </si>
-  <si>
     <t>redirect:/admin/pets
 (flash: message)</t>
   </si>
@@ -1600,21 +1548,6 @@
   </si>
   <si>
     <t>/admin/logs/{logId}</t>
-  </si>
-  <si>
-    <t>/admin/logs/101</t>
-  </si>
-  <si>
-    <t>admin/logs/detail.html
-(model: log,
-relatedPet,
-relatedAction)</t>
-  </si>
-  <si>
-    <t>admin/logs/detail.html
-(model: {log:{logId:101,type:'ALERT'},
-relatedPet:{petId:1,name:'보리'},
-relatedAction:{actionId:301,type:'AUTO_FEED'}})</t>
   </si>
   <si>
     <t>admin-007</t>
@@ -3286,176 +3219,6 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>시스템</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>전체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>로그를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>등급</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>및</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>이벤트별로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>필터링하여</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>조회한다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>선택한</t>
     </r>
     <r>
@@ -3757,14 +3520,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>{ "success", "feedResult", "lastFeedAt", "message" }</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{ "success", "capturedMediaId", "thumbnailUrl", "message" }</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>{ "success", "recordStatus", "message" }</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -3816,18 +3571,6 @@
       </rPr>
       <t>."}</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{success, logList, pageInfo, filter}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"success":true, "logList":[...], "pageInfo":{"total":40}, "filter":{"type":"alert"}}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>petId, name, species, breed, age, weight, gender</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -3845,38 +3588,338 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>name=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>보리&amp;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>age=5&amp;weight=7.5</t>
-    </r>
+    <t>redirect:/admin/pets/{petId}
+(flash: message)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
+    <t>petId=1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>dashboard.html
+(model: pet_name,
+risk_level, temperature
+unread_alert_count)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>dashboard.html
+(model: {pet_name:{petId:1,name:'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>보리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'},
+risk_Level:'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>주의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">', temperature:24.3,
+unread_alert_count:[2])
+</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>petId, enabled(T/F)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>/dashboard/feeder</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>petId=1&amp;feedAmount=30</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "success", "feedStatus", "recordedAt", "message" }</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">dashboard.html
+(model: {petId:1,
+feedStatus:'SUCCESS',
+recordedAt:'2026-03-27 14:10:00',
+message:'30g </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>급여를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>완료했습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.'})</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>/dashboard/snapshot</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "success", "mediaId", "filePath", "createdAt","message" }</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>dashboard.html
+(model: {petId:1,
+mediaId:101,
+filePath:'/images/capture101.jpg',
+createdAt: '2026-03-30 11:30:00',
+message:'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>스냅샷이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>저장되었습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.'})</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>admin-002</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DELETE</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>petId, feedAmount</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{petName, breed, age, userName, device, recentEvent,status}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>petName='</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>보리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'&amp;breed='</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>포메</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'&amp;age=5&amp;userName='</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>차도헌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'&amp;recentEvent='</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>우다다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'&amp;status='</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>경고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
       </rPr>
       <t>성공</t>
     </r>
@@ -3895,30 +3938,53 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF006100"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>정보가 수정되었습니다.')</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>정보가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>수정되었습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.')
 </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FF006100"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
       </rPr>
       <t>실패</t>
     </r>
@@ -3937,9 +4003,10 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF006100"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
       </rPr>
       <t>보리</t>
     </r>
@@ -3959,9 +4026,10 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF006100"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
       </rPr>
       <t>품종을</t>
     </r>
@@ -3979,9 +4047,10 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF006100"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
       </rPr>
       <t>입력해주세요</t>
     </r>
@@ -3998,28 +4067,355 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>redirect:/admin/pets/{petId}
-(flash: message)</t>
+    <r>
+      <t>시스템</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>전체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>로그를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>등급</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이벤트별로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>필터링하여</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>조회한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기본값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>위험</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>등급</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>오늘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>날짜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>petId=1</t>
+    <t>riskLevel, date</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>type, level, date, page?</t>
+    <t>/admin/logs?/today-monitor?riskLevel=DANGER</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>/admin/logs?type=ALERT&amp;level=HIGH</t>
+    <t>{hourlyStats, logList(logId, petName, eventTypeName, severityScore, detectedAt)}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{ "hourlyStats": [0, 1, 0, 4, ...], "logList": [{ "logId": 1, "petName": "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>초코</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>", "eventTypeName": "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>위험구역진입</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>", "severityScore": 80, "detectedAt": "2026-03-30 14:00" }] }</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>filterType, filterValue, rangeType(TODAY, WEEK, MONTH)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>/admin/logs/stats-graph?filterType=EVENT&amp;filterValue=MEAL_SKIPPED&amp;rangeType=TODAY</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>chartLabels(X축 레이블 데이터: "14시" 또는 "03-30" 또는 "3월 4주차"), chartData(각 레이블 발생 건수 숫자 리스트), unit(HOUR, DAY, WEEK 응답 데이터 단위)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "unit": "DAY", "chartLabels": ["03-24", "03-25", "03-26", "03-27", "03-28", "03-29", "03-30"], "chartData": [2, 5, 1, 0, 3, 4, 2] }</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4164,15 +4560,10 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -4999,6 +5390,42 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5014,6 +5441,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5024,56 +5454,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Hyperlink" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="나쁨" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="좋음" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Hyperlink" xfId="3"/>
+    <cellStyle name="나쁨" xfId="2"/>
+    <cellStyle name="좋음" xfId="1"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -5264,7 +5655,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5282,32 +5673,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="73"/>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="85"/>
     </row>
     <row r="2" spans="1:11" ht="17.25" customHeight="1">
-      <c r="A2" s="74"/>
-      <c r="B2" s="75"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="76"/>
+      <c r="A2" s="86"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="87"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="88"/>
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A3" s="2" t="s">
@@ -5415,7 +5806,7 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="56.1" customHeight="1">
-      <c r="A6" s="82" t="s">
+      <c r="A6" s="95" t="s">
         <v>29</v>
       </c>
       <c r="B6" s="32" t="s">
@@ -5450,7 +5841,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A7" s="83"/>
+      <c r="A7" s="96"/>
       <c r="B7" s="17" t="s">
         <v>36</v>
       </c>
@@ -5483,7 +5874,7 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A8" s="83"/>
+      <c r="A8" s="96"/>
       <c r="B8" s="17" t="s">
         <v>44</v>
       </c>
@@ -5516,7 +5907,7 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A9" s="83"/>
+      <c r="A9" s="96"/>
       <c r="B9" s="17" t="s">
         <v>50</v>
       </c>
@@ -5549,7 +5940,7 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A10" s="83"/>
+      <c r="A10" s="96"/>
       <c r="B10" s="17" t="s">
         <v>58</v>
       </c>
@@ -5582,7 +5973,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A11" s="83"/>
+      <c r="A11" s="96"/>
       <c r="B11" s="17" t="s">
         <v>66</v>
       </c>
@@ -5615,7 +6006,7 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="107.25" customHeight="1">
-      <c r="A12" s="83"/>
+      <c r="A12" s="96"/>
       <c r="B12" s="17" t="s">
         <v>74</v>
       </c>
@@ -5648,7 +6039,7 @@
       </c>
     </row>
     <row r="13" spans="1:11" ht="56.1" customHeight="1">
-      <c r="A13" s="83"/>
+      <c r="A13" s="96"/>
       <c r="B13" s="17" t="s">
         <v>81</v>
       </c>
@@ -5681,7 +6072,7 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A14" s="84"/>
+      <c r="A14" s="97"/>
       <c r="B14" s="38" t="s">
         <v>87</v>
       </c>
@@ -5714,7 +6105,7 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="56.1" customHeight="1" thickBot="1">
-      <c r="A15" s="85" t="s">
+      <c r="A15" s="98" t="s">
         <v>95</v>
       </c>
       <c r="B15" s="20" t="s">
@@ -5749,7 +6140,7 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="98.1" customHeight="1">
-      <c r="A16" s="83"/>
+      <c r="A16" s="96"/>
       <c r="B16" s="17" t="s">
         <v>102</v>
       </c>
@@ -5782,7 +6173,7 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A17" s="83"/>
+      <c r="A17" s="96"/>
       <c r="B17" s="17" t="s">
         <v>109</v>
       </c>
@@ -5815,7 +6206,7 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A18" s="83"/>
+      <c r="A18" s="96"/>
       <c r="B18" s="17" t="s">
         <v>115</v>
       </c>
@@ -5848,7 +6239,7 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A19" s="83"/>
+      <c r="A19" s="96"/>
       <c r="B19" s="17" t="s">
         <v>122</v>
       </c>
@@ -5881,7 +6272,7 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A20" s="83"/>
+      <c r="A20" s="96"/>
       <c r="B20" s="17" t="s">
         <v>129</v>
       </c>
@@ -5914,7 +6305,7 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="54.95" customHeight="1">
-      <c r="A21" s="83"/>
+      <c r="A21" s="96"/>
       <c r="B21" s="18" t="s">
         <v>137</v>
       </c>
@@ -5947,1078 +6338,1078 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="98.1" customHeight="1">
-      <c r="A22" s="90" t="s">
-        <v>346</v>
-      </c>
-      <c r="B22" s="99" t="s">
+      <c r="A22" s="100" t="s">
+        <v>332</v>
+      </c>
+      <c r="B22" s="81" t="s">
         <v>143</v>
       </c>
-      <c r="C22" s="99" t="s">
-        <v>347</v>
-      </c>
-      <c r="D22" s="99" t="s">
+      <c r="C22" s="81" t="s">
+        <v>333</v>
+      </c>
+      <c r="D22" s="81" t="s">
         <v>144</v>
       </c>
-      <c r="E22" s="99" t="s">
+      <c r="E22" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="F22" s="99" t="s">
+      <c r="F22" s="81" t="s">
         <v>145</v>
       </c>
-      <c r="G22" s="99" t="s">
+      <c r="G22" s="81" t="s">
         <v>146</v>
       </c>
-      <c r="H22" s="99" t="s">
+      <c r="H22" s="81" t="s">
         <v>147</v>
       </c>
-      <c r="I22" s="99" t="s">
-        <v>148</v>
-      </c>
-      <c r="J22" s="99" t="s">
-        <v>149</v>
-      </c>
-      <c r="K22" s="99" t="s">
+      <c r="I22" s="81" t="s">
+        <v>360</v>
+      </c>
+      <c r="J22" s="81" t="s">
+        <v>361</v>
+      </c>
+      <c r="K22" s="81" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="75">
-      <c r="A23" s="90"/>
-      <c r="B23" s="99" t="s">
+      <c r="A23" s="100"/>
+      <c r="B23" s="81" t="s">
+        <v>148</v>
+      </c>
+      <c r="C23" s="81" t="s">
+        <v>334</v>
+      </c>
+      <c r="D23" s="81" t="s">
+        <v>149</v>
+      </c>
+      <c r="E23" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="C23" s="99" t="s">
-        <v>348</v>
-      </c>
-      <c r="D23" s="99" t="s">
+      <c r="F23" s="81" t="s">
+        <v>335</v>
+      </c>
+      <c r="G23" s="81" t="s">
         <v>151</v>
       </c>
-      <c r="E23" s="99" t="s">
+      <c r="H23" s="81" t="s">
         <v>152</v>
       </c>
-      <c r="F23" s="99" t="s">
+      <c r="I23" s="81" t="s">
         <v>349</v>
       </c>
-      <c r="G23" s="99" t="s">
+      <c r="J23" s="81" t="s">
         <v>153</v>
       </c>
-      <c r="H23" s="99" t="s">
-        <v>154</v>
-      </c>
-      <c r="I23" s="99" t="s">
-        <v>364</v>
-      </c>
-      <c r="J23" s="99" t="s">
-        <v>155</v>
-      </c>
-      <c r="K23" s="99" t="s">
+      <c r="K23" s="81" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A24" s="90"/>
-      <c r="B24" s="99" t="s">
+      <c r="A24" s="100"/>
+      <c r="B24" s="81" t="s">
+        <v>154</v>
+      </c>
+      <c r="C24" s="81" t="s">
+        <v>155</v>
+      </c>
+      <c r="D24" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="C24" s="99" t="s">
+      <c r="E24" s="81" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="81" t="s">
+        <v>336</v>
+      </c>
+      <c r="G24" s="81" t="s">
+        <v>362</v>
+      </c>
+      <c r="H24" s="81" t="s">
         <v>157</v>
       </c>
-      <c r="D24" s="99" t="s">
+      <c r="I24" s="81" t="s">
+        <v>350</v>
+      </c>
+      <c r="J24" s="81" t="s">
         <v>158</v>
       </c>
-      <c r="E24" s="99" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="99" t="s">
-        <v>350</v>
-      </c>
-      <c r="G24" s="99" t="s">
-        <v>159</v>
-      </c>
-      <c r="H24" s="99" t="s">
-        <v>160</v>
-      </c>
-      <c r="I24" s="99" t="s">
-        <v>365</v>
-      </c>
-      <c r="J24" s="99" t="s">
-        <v>161</v>
-      </c>
-      <c r="K24" s="99" t="s">
+      <c r="K24" s="81" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A25" s="90"/>
-      <c r="B25" s="99" t="s">
+      <c r="A25" s="100"/>
+      <c r="B25" s="81" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" s="81" t="s">
+        <v>160</v>
+      </c>
+      <c r="D25" s="81" t="s">
+        <v>161</v>
+      </c>
+      <c r="E25" s="81" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" s="81" t="s">
         <v>162</v>
       </c>
-      <c r="C25" s="99" t="s">
+      <c r="G25" s="81" t="s">
         <v>163</v>
       </c>
-      <c r="D25" s="99" t="s">
+      <c r="H25" s="81" t="s">
         <v>164</v>
       </c>
-      <c r="E25" s="99" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="99" t="s">
+      <c r="I25" s="81" t="s">
+        <v>351</v>
+      </c>
+      <c r="J25" s="81" t="s">
         <v>165</v>
       </c>
-      <c r="G25" s="99" t="s">
-        <v>166</v>
-      </c>
-      <c r="H25" s="99" t="s">
-        <v>167</v>
-      </c>
-      <c r="I25" s="99" t="s">
-        <v>366</v>
-      </c>
-      <c r="J25" s="99" t="s">
-        <v>168</v>
-      </c>
-      <c r="K25" s="99" t="s">
+      <c r="K25" s="81" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="84" customHeight="1">
-      <c r="A26" s="90"/>
-      <c r="B26" s="99" t="s">
-        <v>169</v>
-      </c>
-      <c r="C26" s="99" t="s">
-        <v>170</v>
-      </c>
-      <c r="D26" s="99" t="s">
-        <v>171</v>
-      </c>
-      <c r="E26" s="99" t="s">
+      <c r="A26" s="100"/>
+      <c r="B26" s="81" t="s">
+        <v>166</v>
+      </c>
+      <c r="C26" s="81" t="s">
+        <v>167</v>
+      </c>
+      <c r="D26" s="81" t="s">
+        <v>363</v>
+      </c>
+      <c r="E26" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="F26" s="99" t="s">
-        <v>172</v>
-      </c>
-      <c r="G26" s="99" t="s">
-        <v>173</v>
-      </c>
-      <c r="H26" s="99" t="s">
-        <v>174</v>
-      </c>
-      <c r="I26" s="99" t="s">
-        <v>367</v>
-      </c>
-      <c r="J26" s="99" t="s">
-        <v>175</v>
-      </c>
-      <c r="K26" s="99" t="s">
+      <c r="F26" s="81" t="s">
+        <v>168</v>
+      </c>
+      <c r="G26" s="81" t="s">
+        <v>372</v>
+      </c>
+      <c r="H26" s="81" t="s">
+        <v>364</v>
+      </c>
+      <c r="I26" s="81" t="s">
+        <v>365</v>
+      </c>
+      <c r="J26" s="81" t="s">
+        <v>366</v>
+      </c>
+      <c r="K26" s="81" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="84" customHeight="1">
-      <c r="A27" s="90"/>
-      <c r="B27" s="99" t="s">
-        <v>176</v>
-      </c>
-      <c r="C27" s="99" t="s">
-        <v>177</v>
-      </c>
-      <c r="D27" s="99" t="s">
-        <v>178</v>
-      </c>
-      <c r="E27" s="99" t="s">
+      <c r="A27" s="100"/>
+      <c r="B27" s="81" t="s">
+        <v>169</v>
+      </c>
+      <c r="C27" s="81" t="s">
+        <v>170</v>
+      </c>
+      <c r="D27" s="81" t="s">
+        <v>367</v>
+      </c>
+      <c r="E27" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="F27" s="99" t="s">
-        <v>351</v>
-      </c>
-      <c r="G27" s="99" t="s">
+      <c r="F27" s="81" t="s">
+        <v>337</v>
+      </c>
+      <c r="G27" s="81" t="s">
         <v>146</v>
       </c>
-      <c r="H27" s="99" t="s">
-        <v>179</v>
-      </c>
-      <c r="I27" s="99" t="s">
+      <c r="H27" s="81" t="s">
+        <v>171</v>
+      </c>
+      <c r="I27" s="81" t="s">
         <v>368</v>
       </c>
-      <c r="J27" s="99" t="s">
-        <v>180</v>
-      </c>
-      <c r="K27" s="99" t="s">
+      <c r="J27" s="81" t="s">
+        <v>369</v>
+      </c>
+      <c r="K27" s="81" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A28" s="90"/>
-      <c r="B28" s="91" t="s">
-        <v>181</v>
-      </c>
-      <c r="C28" s="91" t="s">
-        <v>182</v>
-      </c>
-      <c r="D28" s="91" t="s">
-        <v>183</v>
-      </c>
-      <c r="E28" s="91" t="s">
+      <c r="A28" s="100"/>
+      <c r="B28" s="74" t="s">
+        <v>172</v>
+      </c>
+      <c r="C28" s="74" t="s">
+        <v>173</v>
+      </c>
+      <c r="D28" s="74" t="s">
+        <v>174</v>
+      </c>
+      <c r="E28" s="74" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="G28" s="91" t="s">
-        <v>185</v>
-      </c>
-      <c r="H28" s="91" t="s">
-        <v>186</v>
-      </c>
-      <c r="I28" s="99" t="s">
-        <v>369</v>
-      </c>
-      <c r="J28" s="99" t="s">
-        <v>187</v>
-      </c>
-      <c r="K28" s="99" t="s">
+      <c r="F28" s="81" t="s">
+        <v>175</v>
+      </c>
+      <c r="G28" s="74" t="s">
+        <v>176</v>
+      </c>
+      <c r="H28" s="74" t="s">
+        <v>177</v>
+      </c>
+      <c r="I28" s="81" t="s">
+        <v>352</v>
+      </c>
+      <c r="J28" s="81" t="s">
+        <v>178</v>
+      </c>
+      <c r="K28" s="81" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="69.95" customHeight="1" thickBot="1">
-      <c r="A29" s="86" t="s">
-        <v>188</v>
-      </c>
-      <c r="B29" s="87" t="s">
-        <v>189</v>
-      </c>
-      <c r="C29" s="87" t="s">
-        <v>190</v>
-      </c>
-      <c r="D29" s="88" t="s">
-        <v>191</v>
-      </c>
-      <c r="E29" s="87" t="s">
+      <c r="A29" s="92" t="s">
+        <v>179</v>
+      </c>
+      <c r="B29" s="71" t="s">
+        <v>180</v>
+      </c>
+      <c r="C29" s="71" t="s">
+        <v>181</v>
+      </c>
+      <c r="D29" s="72" t="s">
+        <v>182</v>
+      </c>
+      <c r="E29" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="F29" s="87" t="s">
-        <v>192</v>
-      </c>
-      <c r="G29" s="87" t="s">
+      <c r="F29" s="71" t="s">
+        <v>183</v>
+      </c>
+      <c r="G29" s="71" t="s">
         <v>146</v>
       </c>
-      <c r="H29" s="87" t="s">
-        <v>193</v>
-      </c>
-      <c r="I29" s="87" t="s">
-        <v>194</v>
-      </c>
-      <c r="J29" s="87" t="s">
-        <v>195</v>
-      </c>
-      <c r="K29" s="89" t="s">
+      <c r="H29" s="71" t="s">
+        <v>184</v>
+      </c>
+      <c r="I29" s="71" t="s">
+        <v>185</v>
+      </c>
+      <c r="J29" s="71" t="s">
+        <v>186</v>
+      </c>
+      <c r="K29" s="73" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="84" customHeight="1">
-      <c r="A30" s="80"/>
+      <c r="A30" s="93"/>
       <c r="B30" s="21" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="D30" s="57" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="E30" s="21" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="G30" s="21" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="H30" s="21" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="I30" s="21" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="J30" s="21" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A31" s="80"/>
+      <c r="A31" s="93"/>
       <c r="B31" s="21" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="E31" s="21" t="s">
         <v>16</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G31" s="21" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="H31" s="21" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="I31" s="21" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="J31" s="21" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="K31" s="5" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A32" s="81"/>
+      <c r="A32" s="94"/>
       <c r="B32" s="9" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>38</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="98.1" customHeight="1">
-      <c r="A33" s="77" t="s">
-        <v>217</v>
+      <c r="A33" s="89" t="s">
+        <v>208</v>
       </c>
       <c r="B33" s="58" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="C33" s="58" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="D33" s="59" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="E33" s="58" t="s">
         <v>16</v>
       </c>
       <c r="F33" s="58" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="G33" s="58" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="H33" s="58" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="I33" s="58" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="J33" s="58" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="K33" s="60" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="98.1" customHeight="1" thickBot="1">
-      <c r="A34" s="78"/>
+      <c r="A34" s="90"/>
       <c r="B34" s="61" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C34" s="61" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="D34" s="62" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="E34" s="61" t="s">
         <v>16</v>
       </c>
       <c r="F34" s="61" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="G34" s="61" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="H34" s="61" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="I34" s="61" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="J34" s="61" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="K34" s="63" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="69.95" customHeight="1" thickBot="1">
-      <c r="A35" s="77" t="s">
-        <v>233</v>
+      <c r="A35" s="89" t="s">
+        <v>224</v>
       </c>
       <c r="B35" s="58" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="C35" s="58" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="D35" s="59" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="E35" s="58" t="s">
         <v>16</v>
       </c>
       <c r="F35" s="58" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="G35" s="58" t="s">
         <v>18</v>
       </c>
       <c r="H35" s="58" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="I35" s="58" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="J35" s="58" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="K35" s="60" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A36" s="80"/>
+      <c r="A36" s="93"/>
       <c r="B36" s="64" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="C36" s="64" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="D36" s="65" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="E36" s="64" t="s">
         <v>16</v>
       </c>
       <c r="F36" s="64" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G36" s="64" t="s">
         <v>18</v>
       </c>
       <c r="H36" s="64" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="I36" s="64" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="J36" s="64" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="K36" s="66" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="84" customHeight="1">
-      <c r="A37" s="80"/>
+      <c r="A37" s="93"/>
       <c r="B37" s="64" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C37" s="64" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="D37" s="65" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="E37" s="64" t="s">
         <v>38</v>
       </c>
       <c r="F37" s="64" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="G37" s="64" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="H37" s="64" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="I37" s="64" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="J37" s="64" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="K37" s="66" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="69.95" customHeight="1">
-      <c r="A38" s="80"/>
+      <c r="A38" s="93"/>
       <c r="B38" s="64" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="C38" s="64" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="D38" s="65" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="E38" s="64" t="s">
         <v>16</v>
       </c>
       <c r="F38" s="64" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="G38" s="64" t="s">
         <v>18</v>
       </c>
       <c r="H38" s="64" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="I38" s="64" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="J38" s="64" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="K38" s="66" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="84" customHeight="1">
-      <c r="A39" s="80"/>
+      <c r="A39" s="93"/>
       <c r="B39" s="64" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C39" s="64" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="D39" s="65" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="E39" s="64" t="s">
         <v>38</v>
       </c>
       <c r="F39" s="64" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="G39" s="64" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="H39" s="64" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="I39" s="64" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="J39" s="64" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="K39" s="66" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="84" customHeight="1">
-      <c r="A40" s="80"/>
+      <c r="A40" s="93"/>
       <c r="B40" s="64" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="D40" s="65" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="E40" s="64" t="s">
         <v>38</v>
       </c>
       <c r="F40" s="64" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="G40" s="64" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="H40" s="64" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="I40" s="64" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="J40" s="64" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="K40" s="66" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="54.95" customHeight="1">
-      <c r="A41" s="80"/>
+      <c r="A41" s="93"/>
       <c r="B41" s="64" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C41" s="64" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="D41" s="65" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E41" s="64" t="s">
         <v>38</v>
       </c>
       <c r="F41" s="64" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="G41" s="64" t="s">
         <v>146</v>
       </c>
       <c r="H41" s="64" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I41" s="64" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="J41" s="64" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="K41" s="66" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="84" customHeight="1">
-      <c r="A42" s="80"/>
+      <c r="A42" s="93"/>
       <c r="B42" s="64" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C42" s="64" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="D42" s="65" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="E42" s="64" t="s">
         <v>16</v>
       </c>
       <c r="F42" s="64" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="G42" s="64" t="s">
         <v>18</v>
       </c>
       <c r="H42" s="64" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="I42" s="64" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="J42" s="64" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="K42" s="66" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="54.95" customHeight="1">
-      <c r="A43" s="80"/>
+      <c r="A43" s="93"/>
       <c r="B43" s="64" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="C43" s="64" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="D43" s="65" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="E43" s="64" t="s">
         <v>38</v>
       </c>
       <c r="F43" s="64" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="G43" s="64" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="H43" s="64" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="I43" s="64" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="J43" s="64" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="K43" s="66" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="67.5" customHeight="1" thickBot="1">
-      <c r="A44" s="78"/>
-      <c r="B44" s="93" t="s">
-        <v>294</v>
-      </c>
-      <c r="C44" s="93" t="s">
-        <v>295</v>
-      </c>
-      <c r="D44" s="94" t="s">
-        <v>296</v>
-      </c>
-      <c r="E44" s="93" t="s">
+      <c r="A44" s="90"/>
+      <c r="B44" s="75" t="s">
+        <v>285</v>
+      </c>
+      <c r="C44" s="75" t="s">
+        <v>286</v>
+      </c>
+      <c r="D44" s="76" t="s">
+        <v>287</v>
+      </c>
+      <c r="E44" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="F44" s="93" t="s">
+      <c r="F44" s="75" t="s">
+        <v>280</v>
+      </c>
+      <c r="G44" s="75" t="s">
+        <v>288</v>
+      </c>
+      <c r="H44" s="75" t="s">
         <v>289</v>
       </c>
-      <c r="G44" s="93" t="s">
-        <v>297</v>
-      </c>
-      <c r="H44" s="93" t="s">
-        <v>298</v>
-      </c>
-      <c r="I44" s="93" t="s">
-        <v>292</v>
-      </c>
-      <c r="J44" s="93" t="s">
-        <v>299</v>
-      </c>
-      <c r="K44" s="95" t="s">
+      <c r="I44" s="75" t="s">
+        <v>283</v>
+      </c>
+      <c r="J44" s="75" t="s">
+        <v>290</v>
+      </c>
+      <c r="K44" s="77" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="84" customHeight="1">
-      <c r="A45" s="92" t="s">
-        <v>352</v>
-      </c>
-      <c r="B45" s="99" t="s">
-        <v>300</v>
-      </c>
-      <c r="C45" s="99" t="s">
-        <v>301</v>
-      </c>
-      <c r="D45" s="99" t="s">
-        <v>302</v>
-      </c>
-      <c r="E45" s="99" t="s">
+      <c r="A45" s="99" t="s">
+        <v>338</v>
+      </c>
+      <c r="B45" s="81" t="s">
+        <v>291</v>
+      </c>
+      <c r="C45" s="81" t="s">
+        <v>292</v>
+      </c>
+      <c r="D45" s="81" t="s">
+        <v>293</v>
+      </c>
+      <c r="E45" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="F45" s="99" t="s">
-        <v>353</v>
-      </c>
-      <c r="G45" s="99" t="s">
-        <v>303</v>
-      </c>
-      <c r="H45" s="99" t="s">
-        <v>304</v>
-      </c>
-      <c r="I45" s="99" t="s">
-        <v>305</v>
-      </c>
-      <c r="J45" s="99" t="s">
-        <v>306</v>
-      </c>
-      <c r="K45" s="99" t="s">
-        <v>354</v>
+      <c r="F45" s="81" t="s">
+        <v>339</v>
+      </c>
+      <c r="G45" s="81" t="s">
+        <v>294</v>
+      </c>
+      <c r="H45" s="81" t="s">
+        <v>295</v>
+      </c>
+      <c r="I45" s="81" t="s">
+        <v>296</v>
+      </c>
+      <c r="J45" s="81" t="s">
+        <v>297</v>
+      </c>
+      <c r="K45" s="81" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="84" customHeight="1">
-      <c r="A46" s="92"/>
-      <c r="B46" s="99" t="s">
-        <v>308</v>
-      </c>
-      <c r="C46" s="99" t="s">
-        <v>355</v>
-      </c>
-      <c r="D46" s="99" t="s">
-        <v>309</v>
-      </c>
-      <c r="E46" s="99" t="s">
+      <c r="A46" s="99"/>
+      <c r="B46" s="81" t="s">
+        <v>370</v>
+      </c>
+      <c r="C46" s="81" t="s">
+        <v>341</v>
+      </c>
+      <c r="D46" s="81" t="s">
+        <v>299</v>
+      </c>
+      <c r="E46" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="F46" s="99" t="s">
-        <v>356</v>
-      </c>
-      <c r="G46" s="99" t="s">
+      <c r="F46" s="81" t="s">
+        <v>342</v>
+      </c>
+      <c r="G46" s="81" t="s">
         <v>146</v>
       </c>
-      <c r="H46" s="99" t="s">
-        <v>310</v>
-      </c>
-      <c r="I46" s="99" t="s">
-        <v>377</v>
-      </c>
-      <c r="J46" s="99" t="s">
-        <v>311</v>
-      </c>
-      <c r="K46" s="99" t="s">
-        <v>354</v>
+      <c r="H46" s="81" t="s">
+        <v>300</v>
+      </c>
+      <c r="I46" s="81" t="s">
+        <v>357</v>
+      </c>
+      <c r="J46" s="81" t="s">
+        <v>301</v>
+      </c>
+      <c r="K46" s="81" t="s">
+        <v>340</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="97.5">
-      <c r="A47" s="92"/>
-      <c r="B47" s="99" t="s">
-        <v>312</v>
-      </c>
-      <c r="C47" s="99" t="s">
-        <v>357</v>
-      </c>
-      <c r="D47" s="99" t="s">
-        <v>313</v>
-      </c>
-      <c r="E47" s="99" t="s">
+    <row r="47" spans="1:11" ht="90">
+      <c r="A47" s="99"/>
+      <c r="B47" s="81" t="s">
+        <v>302</v>
+      </c>
+      <c r="C47" s="81" t="s">
+        <v>343</v>
+      </c>
+      <c r="D47" s="81" t="s">
+        <v>303</v>
+      </c>
+      <c r="E47" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="F47" s="99" t="s">
+      <c r="F47" s="81" t="s">
+        <v>344</v>
+      </c>
+      <c r="G47" s="81" t="s">
+        <v>373</v>
+      </c>
+      <c r="H47" s="81" t="s">
+        <v>374</v>
+      </c>
+      <c r="I47" s="81" t="s">
         <v>358</v>
       </c>
-      <c r="G47" s="99" t="s">
-        <v>374</v>
-      </c>
-      <c r="H47" s="99" t="s">
-        <v>378</v>
-      </c>
-      <c r="I47" s="99" t="s">
-        <v>380</v>
-      </c>
-      <c r="J47" s="100" t="s">
-        <v>379</v>
-      </c>
-      <c r="K47" s="99" t="s">
-        <v>354</v>
+      <c r="J47" s="81" t="s">
+        <v>375</v>
+      </c>
+      <c r="K47" s="81" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="54.95" customHeight="1">
-      <c r="A48" s="92"/>
-      <c r="B48" s="99" t="s">
-        <v>314</v>
-      </c>
-      <c r="C48" s="99" t="s">
+      <c r="A48" s="99"/>
+      <c r="B48" s="81" t="s">
+        <v>304</v>
+      </c>
+      <c r="C48" s="81" t="s">
+        <v>345</v>
+      </c>
+      <c r="D48" s="81" t="s">
+        <v>305</v>
+      </c>
+      <c r="E48" s="82" t="s">
+        <v>371</v>
+      </c>
+      <c r="F48" s="81" t="s">
+        <v>346</v>
+      </c>
+      <c r="G48" s="81" t="s">
+        <v>356</v>
+      </c>
+      <c r="H48" s="81" t="s">
         <v>359</v>
       </c>
-      <c r="D48" s="99" t="s">
-        <v>315</v>
-      </c>
-      <c r="E48" s="99" t="s">
-        <v>38</v>
-      </c>
-      <c r="F48" s="99" t="s">
-        <v>360</v>
-      </c>
-      <c r="G48" s="99" t="s">
-        <v>376</v>
-      </c>
-      <c r="H48" s="99" t="s">
-        <v>381</v>
-      </c>
-      <c r="I48" s="99" t="s">
-        <v>317</v>
-      </c>
-      <c r="J48" s="99" t="s">
-        <v>318</v>
-      </c>
-      <c r="K48" s="99" t="s">
-        <v>354</v>
+      <c r="I48" s="81" t="s">
+        <v>306</v>
+      </c>
+      <c r="J48" s="81" t="s">
+        <v>307</v>
+      </c>
+      <c r="K48" s="81" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="84" customHeight="1">
-      <c r="A49" s="92"/>
-      <c r="B49" s="99" t="s">
-        <v>319</v>
-      </c>
-      <c r="C49" s="99" t="s">
-        <v>320</v>
-      </c>
-      <c r="D49" s="99" t="s">
-        <v>321</v>
-      </c>
-      <c r="E49" s="99" t="s">
+      <c r="A49" s="99"/>
+      <c r="B49" s="81" t="s">
+        <v>308</v>
+      </c>
+      <c r="C49" s="81" t="s">
+        <v>309</v>
+      </c>
+      <c r="D49" s="81" t="s">
+        <v>310</v>
+      </c>
+      <c r="E49" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="F49" s="99" t="s">
-        <v>361</v>
-      </c>
-      <c r="G49" s="99" t="s">
+      <c r="F49" s="82" t="s">
+        <v>376</v>
+      </c>
+      <c r="G49" s="81" t="s">
+        <v>377</v>
+      </c>
+      <c r="H49" s="81" t="s">
+        <v>378</v>
+      </c>
+      <c r="I49" s="81" t="s">
+        <v>379</v>
+      </c>
+      <c r="J49" s="81" t="s">
+        <v>380</v>
+      </c>
+      <c r="K49" s="81" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="90">
+      <c r="A50" s="99"/>
+      <c r="B50" s="81" t="s">
+        <v>311</v>
+      </c>
+      <c r="C50" s="81" t="s">
+        <v>312</v>
+      </c>
+      <c r="D50" s="81" t="s">
+        <v>313</v>
+      </c>
+      <c r="E50" s="81" t="s">
+        <v>16</v>
+      </c>
+      <c r="F50" s="81" t="s">
+        <v>347</v>
+      </c>
+      <c r="G50" s="81" t="s">
+        <v>381</v>
+      </c>
+      <c r="H50" s="81" t="s">
         <v>382</v>
       </c>
-      <c r="H49" s="99" t="s">
+      <c r="I50" s="82" t="s">
         <v>383</v>
       </c>
-      <c r="I49" s="99" t="s">
-        <v>372</v>
-      </c>
-      <c r="J49" s="99" t="s">
-        <v>373</v>
-      </c>
-      <c r="K49" s="99" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="84" customHeight="1">
-      <c r="A50" s="92"/>
-      <c r="B50" s="99" t="s">
-        <v>322</v>
-      </c>
-      <c r="C50" s="99" t="s">
-        <v>323</v>
-      </c>
-      <c r="D50" s="99" t="s">
-        <v>324</v>
-      </c>
-      <c r="E50" s="99" t="s">
-        <v>16</v>
-      </c>
-      <c r="F50" s="99" t="s">
-        <v>362</v>
-      </c>
-      <c r="G50" s="99" t="s">
-        <v>316</v>
-      </c>
-      <c r="H50" s="99" t="s">
-        <v>325</v>
-      </c>
-      <c r="I50" s="99" t="s">
-        <v>326</v>
-      </c>
-      <c r="J50" s="99" t="s">
-        <v>327</v>
-      </c>
-      <c r="K50" s="99" t="s">
-        <v>354</v>
+      <c r="J50" s="81" t="s">
+        <v>384</v>
+      </c>
+      <c r="K50" s="81" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A51" s="92"/>
-      <c r="B51" s="99" t="s">
-        <v>328</v>
-      </c>
-      <c r="C51" s="99" t="s">
-        <v>329</v>
-      </c>
-      <c r="D51" s="99" t="s">
-        <v>330</v>
-      </c>
-      <c r="E51" s="99" t="s">
+      <c r="A51" s="99"/>
+      <c r="B51" s="81" t="s">
+        <v>314</v>
+      </c>
+      <c r="C51" s="81" t="s">
+        <v>315</v>
+      </c>
+      <c r="D51" s="81" t="s">
+        <v>316</v>
+      </c>
+      <c r="E51" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="F51" s="99" t="s">
-        <v>363</v>
-      </c>
-      <c r="G51" s="99" t="s">
-        <v>375</v>
-      </c>
-      <c r="H51" s="99" t="s">
-        <v>331</v>
-      </c>
-      <c r="I51" s="99" t="s">
-        <v>370</v>
-      </c>
-      <c r="J51" s="99" t="s">
-        <v>371</v>
-      </c>
-      <c r="K51" s="99" t="s">
+      <c r="F51" s="81" t="s">
+        <v>348</v>
+      </c>
+      <c r="G51" s="81" t="s">
+        <v>355</v>
+      </c>
+      <c r="H51" s="81" t="s">
+        <v>317</v>
+      </c>
+      <c r="I51" s="81" t="s">
+        <v>353</v>
+      </c>
+      <c r="J51" s="81" t="s">
         <v>354</v>
+      </c>
+      <c r="K51" s="81" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="52" spans="1:11" s="8" customFormat="1" ht="69.95" customHeight="1" thickBot="1">
-      <c r="A52" s="77" t="s">
-        <v>332</v>
-      </c>
-      <c r="B52" s="96" t="s">
-        <v>333</v>
-      </c>
-      <c r="C52" s="96" t="s">
-        <v>334</v>
-      </c>
-      <c r="D52" s="97" t="s">
-        <v>335</v>
-      </c>
-      <c r="E52" s="96" t="s">
+      <c r="A52" s="89" t="s">
+        <v>318</v>
+      </c>
+      <c r="B52" s="78" t="s">
+        <v>319</v>
+      </c>
+      <c r="C52" s="78" t="s">
+        <v>320</v>
+      </c>
+      <c r="D52" s="79" t="s">
+        <v>321</v>
+      </c>
+      <c r="E52" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="F52" s="96" t="s">
-        <v>336</v>
-      </c>
-      <c r="G52" s="96" t="s">
+      <c r="F52" s="78" t="s">
+        <v>322</v>
+      </c>
+      <c r="G52" s="78" t="s">
         <v>146</v>
       </c>
-      <c r="H52" s="96" t="s">
-        <v>337</v>
-      </c>
-      <c r="I52" s="96" t="s">
-        <v>338</v>
-      </c>
-      <c r="J52" s="96" t="s">
-        <v>339</v>
-      </c>
-      <c r="K52" s="98" t="s">
-        <v>307</v>
+      <c r="H52" s="78" t="s">
+        <v>323</v>
+      </c>
+      <c r="I52" s="78" t="s">
+        <v>324</v>
+      </c>
+      <c r="J52" s="78" t="s">
+        <v>325</v>
+      </c>
+      <c r="K52" s="80" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="56.1" customHeight="1" thickBot="1">
-      <c r="A53" s="78"/>
+      <c r="A53" s="90"/>
       <c r="B53" s="61" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="C53" s="61" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="D53" s="62" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="E53" s="61" t="s">
         <v>38</v>
       </c>
       <c r="F53" s="61" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="G53" s="61" t="s">
         <v>146</v>
       </c>
       <c r="H53" s="61" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I53" s="61" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="J53" s="61" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="K53" s="63" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="75.75" customHeight="1">
-      <c r="A54" s="79"/>
+      <c r="A54" s="91"/>
     </row>
     <row r="55" spans="1:11" ht="54.95" customHeight="1">
-      <c r="A55" s="79"/>
+      <c r="A55" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -7035,7 +7426,7 @@
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>